--- a/optimized_version/metadata/validation_daily_metrics/agus6_validation_daily_metrics.xlsx
+++ b/optimized_version/metadata/validation_daily_metrics/agus6_validation_daily_metrics.xlsx
@@ -467,7 +467,7 @@
         <v>45676</v>
       </c>
       <c r="B2" t="n">
-        <v>0.4057982857199856</v>
+        <v>0.4098384367763053</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -476,10 +476,10 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6996838970109707</v>
+        <v>0.7066499901046939</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6996838970109707</v>
+        <v>0.7066499901046939</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
@@ -491,7 +491,7 @@
         <v>45677</v>
       </c>
       <c r="B3" t="n">
-        <v>7.094076242810727</v>
+        <v>7.093870371178868</v>
       </c>
       <c r="C3" t="n">
         <v>24</v>
@@ -500,13 +500,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>10.61837083333334</v>
+        <v>10.61837083333335</v>
       </c>
       <c r="F3" t="n">
-        <v>17.59790161220191</v>
+        <v>17.59718031805072</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5100798116903218</v>
+        <v>0.5101199720835492</v>
       </c>
       <c r="H3" t="n">
         <v>24</v>
@@ -517,7 +517,7 @@
         <v>45678</v>
       </c>
       <c r="B4" t="n">
-        <v>6.206031984614299</v>
+        <v>6.20537495853778</v>
       </c>
       <c r="C4" t="n">
         <v>24</v>
@@ -526,13 +526,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>8.509126341915744</v>
+        <v>8.508545834157934</v>
       </c>
       <c r="F4" t="n">
-        <v>16.85908108441852</v>
+        <v>16.85970636483076</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6545065601388187</v>
+        <v>0.6544809318989928</v>
       </c>
       <c r="H4" t="n">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>45679</v>
       </c>
       <c r="B5" t="n">
-        <v>1.754436625167988</v>
+        <v>1.754441324682608</v>
       </c>
       <c r="C5" t="n">
         <v>24</v>
@@ -552,13 +552,13 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>2.965254166666667</v>
+        <v>2.965254166666673</v>
       </c>
       <c r="F5" t="n">
-        <v>5.518974374987605</v>
+        <v>5.520270494884259</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8240228579087775</v>
+        <v>0.823940192455865</v>
       </c>
       <c r="H5" t="n">
         <v>24</v>
@@ -569,7 +569,7 @@
         <v>45680</v>
       </c>
       <c r="B6" t="n">
-        <v>1.744318256642505</v>
+        <v>1.744309650708601</v>
       </c>
       <c r="C6" t="n">
         <v>24</v>
@@ -581,10 +581,10 @@
         <v>3.168779166666675</v>
       </c>
       <c r="F6" t="n">
-        <v>5.00796995472806</v>
+        <v>5.007771843619645</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.02988647145018386</v>
+        <v>-0.02980499016472149</v>
       </c>
       <c r="H6" t="n">
         <v>24</v>
@@ -595,7 +595,7 @@
         <v>45681</v>
       </c>
       <c r="B7" t="n">
-        <v>0.6323633158401093</v>
+        <v>0.6323561432060962</v>
       </c>
       <c r="C7" t="n">
         <v>24</v>
@@ -604,13 +604,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1.170760416666666</v>
+        <v>1.170760416666668</v>
       </c>
       <c r="F7" t="n">
-        <v>2.106638986356334</v>
+        <v>2.106747204225634</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1336080862148709</v>
+        <v>0.1335190709676511</v>
       </c>
       <c r="H7" t="n">
         <v>24</v>
@@ -621,7 +621,7 @@
         <v>45682</v>
       </c>
       <c r="B8" t="n">
-        <v>5.152925839001329</v>
+        <v>5.152118223546407</v>
       </c>
       <c r="C8" t="n">
         <v>24</v>
@@ -630,13 +630,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>4.586621433831515</v>
+        <v>4.585460418315893</v>
       </c>
       <c r="F8" t="n">
-        <v>20.22489143929639</v>
+        <v>20.22339401105266</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6454108373679639</v>
+        <v>0.6454633421907818</v>
       </c>
       <c r="H8" t="n">
         <v>24</v>
@@ -647,7 +647,7 @@
         <v>45683</v>
       </c>
       <c r="B9" t="n">
-        <v>3.491358994405781</v>
+        <v>3.492493198708572</v>
       </c>
       <c r="C9" t="n">
         <v>24</v>
@@ -656,13 +656,13 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>6.044433474252748</v>
+        <v>6.046174997526176</v>
       </c>
       <c r="F9" t="n">
-        <v>17.66198994433749</v>
+        <v>17.66381591151254</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3718004167329274</v>
+        <v>0.3716705184466663</v>
       </c>
       <c r="H9" t="n">
         <v>24</v>
@@ -673,7 +673,7 @@
         <v>45684</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4617209515559097</v>
+        <v>0.4614155494338943</v>
       </c>
       <c r="C10" t="n">
         <v>24</v>
@@ -682,13 +682,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8735846752490831</v>
+        <v>0.8730041674912693</v>
       </c>
       <c r="F10" t="n">
-        <v>1.566158532019724</v>
+        <v>1.564313612928504</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7027354747482848</v>
+        <v>0.7034354115230561</v>
       </c>
       <c r="H10" t="n">
         <v>24</v>
@@ -699,7 +699,7 @@
         <v>45685</v>
       </c>
       <c r="B11" t="n">
-        <v>1.454984234680431</v>
+        <v>1.456176692147493</v>
       </c>
       <c r="C11" t="n">
         <v>24</v>
@@ -708,13 +708,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>2.682315465670328</v>
+        <v>2.684637496701566</v>
       </c>
       <c r="F11" t="n">
-        <v>4.097690513118537</v>
+        <v>4.098609666787985</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7216916977751215</v>
+        <v>0.7215668290049749</v>
       </c>
       <c r="H11" t="n">
         <v>24</v>
@@ -725,7 +725,7 @@
         <v>45686</v>
       </c>
       <c r="B12" t="n">
-        <v>1.808975025418224</v>
+        <v>1.808669429938</v>
       </c>
       <c r="C12" t="n">
         <v>24</v>
@@ -734,13 +734,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>3.170468008582416</v>
+        <v>3.169887500824609</v>
       </c>
       <c r="F12" t="n">
-        <v>5.529426025111764</v>
+        <v>5.529236355990803</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8768690848411657</v>
+        <v>0.8768775319138966</v>
       </c>
       <c r="H12" t="n">
         <v>24</v>
@@ -751,7 +751,7 @@
         <v>45687</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1629781945913036</v>
+        <v>0.1635776435675619</v>
       </c>
       <c r="C13" t="n">
         <v>24</v>
@@ -760,13 +760,13 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3146723161684915</v>
+        <v>0.3158333316841109</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3945523262694331</v>
+        <v>0.3951241082955356</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1044730169818705</v>
+        <v>0.1018755553764855</v>
       </c>
       <c r="H13" t="n">
         <v>24</v>
@@ -777,7 +777,7 @@
         <v>45688</v>
       </c>
       <c r="B14" t="n">
-        <v>2.694617434277437</v>
+        <v>2.694622183689466</v>
       </c>
       <c r="C14" t="n">
         <v>24</v>
@@ -786,13 +786,13 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>4.706845833333333</v>
+        <v>4.706845833333335</v>
       </c>
       <c r="F14" t="n">
-        <v>8.338611818312918</v>
+        <v>8.338257262911531</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5642871808153536</v>
+        <v>0.5643242327977571</v>
       </c>
       <c r="H14" t="n">
         <v>24</v>
@@ -803,7 +803,7 @@
         <v>45689</v>
       </c>
       <c r="B15" t="n">
-        <v>1.162829553884383</v>
+        <v>1.16155867045783</v>
       </c>
       <c r="C15" t="n">
         <v>24</v>
@@ -812,13 +812,13 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>2.143622034329674</v>
+        <v>2.141300003298438</v>
       </c>
       <c r="F15" t="n">
-        <v>3.083818428095142</v>
+        <v>3.083172847078396</v>
       </c>
       <c r="G15" t="n">
-        <v>0.444875173782157</v>
+        <v>0.4451075743244164</v>
       </c>
       <c r="H15" t="n">
         <v>24</v>
@@ -829,7 +829,7 @@
         <v>45690</v>
       </c>
       <c r="B16" t="n">
-        <v>9.846535772787989</v>
+        <v>9.847088692076786</v>
       </c>
       <c r="C16" t="n">
         <v>24</v>
@@ -838,13 +838,13 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>13.13947097425275</v>
+        <v>13.14121249752617</v>
       </c>
       <c r="F16" t="n">
-        <v>24.73135651362741</v>
+        <v>24.73151149301316</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5498402907835935</v>
+        <v>0.5498346489018975</v>
       </c>
       <c r="H16" t="n">
         <v>24</v>
@@ -855,7 +855,7 @@
         <v>45691</v>
       </c>
       <c r="B17" t="n">
-        <v>0.2699546635460567</v>
+        <v>0.2699365583203097</v>
       </c>
       <c r="C17" t="n">
         <v>24</v>
@@ -864,13 +864,13 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5067971752490786</v>
+        <v>0.5067708333333284</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8315154832194128</v>
+        <v>0.8309929439121355</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3418460966024175</v>
+        <v>-0.3401601459957311</v>
       </c>
       <c r="H17" t="n">
         <v>24</v>
@@ -881,7 +881,7 @@
         <v>45692</v>
       </c>
       <c r="B18" t="n">
-        <v>1.106899331450266</v>
+        <v>1.106558736846254</v>
       </c>
       <c r="C18" t="n">
         <v>24</v>
@@ -890,13 +890,13 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>2.021363841915752</v>
+        <v>2.020783334157944</v>
       </c>
       <c r="F18" t="n">
-        <v>4.038683154921052</v>
+        <v>4.038648378108296</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4754666906323253</v>
+        <v>-0.4754412804647348</v>
       </c>
       <c r="H18" t="n">
         <v>24</v>
@@ -907,7 +907,7 @@
         <v>45693</v>
       </c>
       <c r="B19" t="n">
-        <v>2.459356534461736</v>
+        <v>2.459983660376677</v>
       </c>
       <c r="C19" t="n">
         <v>24</v>
@@ -916,13 +916,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>4.128797316168503</v>
+        <v>4.129958331684123</v>
       </c>
       <c r="F19" t="n">
-        <v>8.325759072279411</v>
+        <v>8.32556854867007</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2626435919867358</v>
+        <v>0.2626773383864613</v>
       </c>
       <c r="H19" t="n">
         <v>24</v>
@@ -933,7 +933,7 @@
         <v>45694</v>
       </c>
       <c r="B20" t="n">
-        <v>3.677917301441361</v>
+        <v>3.677184854108761</v>
       </c>
       <c r="C20" t="n">
         <v>24</v>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>6.106616572720394</v>
+        <v>6.105455557204778</v>
       </c>
       <c r="F20" t="n">
-        <v>7.88628793156028</v>
+        <v>7.885272920400323</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6346603721141308</v>
+        <v>0.6347544087354428</v>
       </c>
       <c r="H20" t="n">
         <v>24</v>
@@ -959,7 +959,7 @@
         <v>45695</v>
       </c>
       <c r="B21" t="n">
-        <v>3.495339157406979</v>
+        <v>3.496197151058458</v>
       </c>
       <c r="C21" t="n">
         <v>24</v>
@@ -968,13 +968,13 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>5.821170974252738</v>
+        <v>5.822912497526165</v>
       </c>
       <c r="F21" t="n">
-        <v>9.207851118289177</v>
+        <v>9.209050131755637</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6563774944882111</v>
+        <v>0.6562879980723157</v>
       </c>
       <c r="H21" t="n">
         <v>24</v>
@@ -985,7 +985,7 @@
         <v>45696</v>
       </c>
       <c r="B22" t="n">
-        <v>3.351239180880428</v>
+        <v>3.351572242135043</v>
       </c>
       <c r="C22" t="n">
         <v>24</v>
@@ -994,13 +994,13 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>5.581794491417583</v>
+        <v>5.582374999175395</v>
       </c>
       <c r="F22" t="n">
-        <v>8.63367565316803</v>
+        <v>8.633655905681394</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7738696822779974</v>
+        <v>0.7738707167158196</v>
       </c>
       <c r="H22" t="n">
         <v>24</v>
@@ -1011,7 +1011,7 @@
         <v>45697</v>
       </c>
       <c r="B23" t="n">
-        <v>9.237480422082463</v>
+        <v>9.235977965186541</v>
       </c>
       <c r="C23" t="n">
         <v>24</v>
@@ -1020,13 +1020,13 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>12.80487620099634</v>
+        <v>12.80304166914049</v>
       </c>
       <c r="F23" t="n">
-        <v>19.72851537228971</v>
+        <v>19.72780772104045</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3855669731585809</v>
+        <v>0.385611051133302</v>
       </c>
       <c r="H23" t="n">
         <v>24</v>
@@ -1037,7 +1037,7 @@
         <v>45698</v>
       </c>
       <c r="B24" t="n">
-        <v>2.633546983619779</v>
+        <v>2.633510230336097</v>
       </c>
       <c r="C24" t="n">
         <v>24</v>
@@ -1049,10 +1049,10 @@
         <v>4.408404166666667</v>
       </c>
       <c r="F24" t="n">
-        <v>6.364306786805662</v>
+        <v>6.366445341626999</v>
       </c>
       <c r="G24" t="n">
-        <v>0.8433807334595792</v>
+        <v>0.843275460356815</v>
       </c>
       <c r="H24" t="n">
         <v>24</v>
@@ -1063,7 +1063,7 @@
         <v>45699</v>
       </c>
       <c r="B25" t="n">
-        <v>4.247023516113516</v>
+        <v>4.246786038112093</v>
       </c>
       <c r="C25" t="n">
         <v>24</v>
@@ -1072,13 +1072,13 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>6.865363841915751</v>
+        <v>6.864783334157944</v>
       </c>
       <c r="F25" t="n">
-        <v>11.02138860418486</v>
+        <v>11.02096953787275</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5626397351868139</v>
+        <v>0.5626729940574225</v>
       </c>
       <c r="H25" t="n">
         <v>24</v>
@@ -1089,7 +1089,7 @@
         <v>45700</v>
       </c>
       <c r="B26" t="n">
-        <v>3.317180340714152</v>
+        <v>3.317078980750245</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
@@ -1098,13 +1098,13 @@
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>5.078654166666663</v>
+        <v>5.078654166666657</v>
       </c>
       <c r="F26" t="n">
-        <v>7.599454584857336</v>
+        <v>7.598656673528351</v>
       </c>
       <c r="G26" t="n">
-        <v>0.5550420652163097</v>
+        <v>0.5551354978000337</v>
       </c>
       <c r="H26" t="n">
         <v>24</v>
@@ -1115,7 +1115,7 @@
         <v>45701</v>
       </c>
       <c r="B27" t="n">
-        <v>0.7242526437652115</v>
+        <v>0.7250059641005037</v>
       </c>
       <c r="C27" t="n">
         <v>24</v>
@@ -1124,13 +1124,13 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>1.080493149501831</v>
+        <v>1.08165416501745</v>
       </c>
       <c r="F27" t="n">
-        <v>2.212257159115325</v>
+        <v>2.211888699297505</v>
       </c>
       <c r="G27" t="n">
-        <v>-1.023972386539141</v>
+        <v>-1.023298242134372</v>
       </c>
       <c r="H27" t="n">
         <v>24</v>
@@ -1141,7 +1141,7 @@
         <v>45702</v>
       </c>
       <c r="B28" t="n">
-        <v>2.949492013357463</v>
+        <v>2.949392453909811</v>
       </c>
       <c r="C28" t="n">
         <v>24</v>
@@ -1150,13 +1150,13 @@
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>4.511629166666673</v>
+        <v>4.511629166666668</v>
       </c>
       <c r="F28" t="n">
-        <v>7.341952483790458</v>
+        <v>7.341735152727696</v>
       </c>
       <c r="G28" t="n">
-        <v>0.3096650558025803</v>
+        <v>0.309705924769482</v>
       </c>
       <c r="H28" t="n">
         <v>24</v>
@@ -1167,7 +1167,7 @@
         <v>45703</v>
       </c>
       <c r="B29" t="n">
-        <v>0.90607621406135</v>
+        <v>0.9060625897535898</v>
       </c>
       <c r="C29" t="n">
         <v>24</v>
@@ -1176,13 +1176,13 @@
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>1.357887499999996</v>
+        <v>1.357887499999998</v>
       </c>
       <c r="F29" t="n">
-        <v>1.992665257646812</v>
+        <v>1.993189467778471</v>
       </c>
       <c r="G29" t="n">
-        <v>0.250004649230207</v>
+        <v>0.2496099950114972</v>
       </c>
       <c r="H29" t="n">
         <v>24</v>
@@ -1193,7 +1193,7 @@
         <v>45704</v>
       </c>
       <c r="B30" t="n">
-        <v>2.927324451721292</v>
+        <v>2.928448629569478</v>
       </c>
       <c r="C30" t="n">
         <v>24</v>
@@ -1202,13 +1202,13 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>4.067757140919418</v>
+        <v>4.06949866419285</v>
       </c>
       <c r="F30" t="n">
-        <v>7.056630927522574</v>
+        <v>7.056676212749946</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.1764085925449492</v>
+        <v>-0.1764236915637536</v>
       </c>
       <c r="H30" t="n">
         <v>24</v>
@@ -1219,7 +1219,7 @@
         <v>45705</v>
       </c>
       <c r="B31" t="n">
-        <v>0.5197756946125176</v>
+        <v>0.5241573700474392</v>
       </c>
       <c r="C31" t="n">
         <v>24</v>
@@ -1228,13 +1228,13 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.8263518970109823</v>
+        <v>0.83331798997857</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8263518970109823</v>
+        <v>0.83331798997857</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9791463920246226</v>
+        <v>0.9787933209588127</v>
       </c>
       <c r="H31" t="n">
         <v>24</v>
@@ -1245,7 +1245,7 @@
         <v>45706</v>
       </c>
       <c r="B32" t="n">
-        <v>0.8384495479526544</v>
+        <v>0.8392756249108254</v>
       </c>
       <c r="C32" t="n">
         <v>24</v>
@@ -1254,13 +1254,13 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>1.399280649501819</v>
+        <v>1.400737497526161</v>
       </c>
       <c r="F32" t="n">
-        <v>2.034895680263938</v>
+        <v>2.035836419507035</v>
       </c>
       <c r="G32" t="n">
-        <v>0.6055403210405634</v>
+        <v>0.605175516613438</v>
       </c>
       <c r="H32" t="n">
         <v>24</v>
@@ -1271,7 +1271,7 @@
         <v>45707</v>
       </c>
       <c r="B33" t="n">
-        <v>2.241348951487572</v>
+        <v>2.241615477311561</v>
       </c>
       <c r="C33" t="n">
         <v>24</v>
@@ -1280,13 +1280,13 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>3.580902824750916</v>
+        <v>3.581483332508721</v>
       </c>
       <c r="F33" t="n">
-        <v>6.18461518402176</v>
+        <v>6.18504037469657</v>
       </c>
       <c r="G33" t="n">
-        <v>0.717277001560239</v>
+        <v>0.7172381259596858</v>
       </c>
       <c r="H33" t="n">
         <v>24</v>
@@ -1297,7 +1297,7 @@
         <v>45708</v>
       </c>
       <c r="B34" t="n">
-        <v>1.566905258533958</v>
+        <v>1.565564378727879</v>
       </c>
       <c r="C34" t="n">
         <v>24</v>
@@ -1306,13 +1306,13 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>2.569592867663007</v>
+        <v>2.567270836631765</v>
       </c>
       <c r="F34" t="n">
-        <v>5.489422760377734</v>
+        <v>5.4884223727951</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5984756946903556</v>
+        <v>0.5986220282287954</v>
       </c>
       <c r="H34" t="n">
         <v>24</v>
@@ -1323,7 +1323,7 @@
         <v>45709</v>
       </c>
       <c r="B35" t="n">
-        <v>2.302705120982389</v>
+        <v>2.302752725583315</v>
       </c>
       <c r="C35" t="n">
         <v>24</v>
@@ -1332,13 +1332,13 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>3.587454166666662</v>
+        <v>3.587454166666665</v>
       </c>
       <c r="F35" t="n">
-        <v>5.73888078492678</v>
+        <v>5.737578888410883</v>
       </c>
       <c r="G35" t="n">
-        <v>0.769144503705698</v>
+        <v>0.7692492334907766</v>
       </c>
       <c r="H35" t="n">
         <v>24</v>
@@ -1349,7 +1349,7 @@
         <v>45710</v>
       </c>
       <c r="B36" t="n">
-        <v>2.636816435702324</v>
+        <v>2.636489898568224</v>
       </c>
       <c r="C36" t="n">
         <v>24</v>
@@ -1358,13 +1358,13 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>4.460168008582413</v>
+        <v>4.459587500824605</v>
       </c>
       <c r="F36" t="n">
-        <v>6.702129705819329</v>
+        <v>6.703475435993743</v>
       </c>
       <c r="G36" t="n">
-        <v>0.1990240239740918</v>
+        <v>0.198702333465693</v>
       </c>
       <c r="H36" t="n">
         <v>24</v>
@@ -1375,7 +1375,7 @@
         <v>45711</v>
       </c>
       <c r="B37" t="n">
-        <v>2.671821191895741</v>
+        <v>2.67175656334641</v>
       </c>
       <c r="C37" t="n">
         <v>24</v>
@@ -1384,13 +1384,13 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>4.197066666666669</v>
+        <v>4.197066666686062</v>
       </c>
       <c r="F37" t="n">
-        <v>7.639446530027987</v>
+        <v>7.639230823343818</v>
       </c>
       <c r="G37" t="n">
-        <v>0.7092012293921525</v>
+        <v>0.7092176510930549</v>
       </c>
       <c r="H37" t="n">
         <v>24</v>
@@ -1401,7 +1401,7 @@
         <v>45712</v>
       </c>
       <c r="B38" t="n">
-        <v>2.921274863238801</v>
+        <v>2.920884993679065</v>
       </c>
       <c r="C38" t="n">
         <v>24</v>
@@ -1410,13 +1410,13 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>4.584838841915754</v>
+        <v>4.584258334157944</v>
       </c>
       <c r="F38" t="n">
-        <v>6.553316506773006</v>
+        <v>6.553267720191659</v>
       </c>
       <c r="G38" t="n">
-        <v>0.6168813490467451</v>
+        <v>0.616887053327818</v>
       </c>
       <c r="H38" t="n">
         <v>24</v>
@@ -1427,7 +1427,7 @@
         <v>45713</v>
       </c>
       <c r="B39" t="n">
-        <v>2.191211048329392</v>
+        <v>2.189587673452402</v>
       </c>
       <c r="C39" t="n">
         <v>24</v>
@@ -1436,13 +1436,13 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>3.066534534329671</v>
+        <v>3.064212503298438</v>
       </c>
       <c r="F39" t="n">
-        <v>5.252413096973601</v>
+        <v>5.250703279683045</v>
       </c>
       <c r="G39" t="n">
-        <v>0.7010537912486472</v>
+        <v>0.7012483914032865</v>
       </c>
       <c r="H39" t="n">
         <v>24</v>
@@ -1453,7 +1453,7 @@
         <v>45714</v>
       </c>
       <c r="B40" t="n">
-        <v>1.581354288512271</v>
+        <v>1.58184681258601</v>
       </c>
       <c r="C40" t="n">
         <v>24</v>
@@ -1462,13 +1462,13 @@
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>2.583994491417585</v>
+        <v>2.584574999175396</v>
       </c>
       <c r="F40" t="n">
-        <v>4.62692626767349</v>
+        <v>4.630127144439356</v>
       </c>
       <c r="G40" t="n">
-        <v>0.9447490634183124</v>
+        <v>0.9446725925167739</v>
       </c>
       <c r="H40" t="n">
         <v>24</v>
@@ -1479,7 +1479,7 @@
         <v>45715</v>
       </c>
       <c r="B41" t="n">
-        <v>2.66519683327147</v>
+        <v>2.664720719119697</v>
       </c>
       <c r="C41" t="n">
         <v>24</v>
@@ -1488,13 +1488,13 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>4.476581850498168</v>
+        <v>4.475825000824609</v>
       </c>
       <c r="F41" t="n">
-        <v>8.709130553425441</v>
+        <v>8.708646487700662</v>
       </c>
       <c r="G41" t="n">
-        <v>0.4526354220447637</v>
+        <v>0.4526962669399194</v>
       </c>
       <c r="H41" t="n">
         <v>24</v>
@@ -1505,7 +1505,7 @@
         <v>45716</v>
       </c>
       <c r="B42" t="n">
-        <v>3.722198562134265</v>
+        <v>3.721471989789384</v>
       </c>
       <c r="C42" t="n">
         <v>24</v>
@@ -1514,13 +1514,13 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>6.069502683831501</v>
+        <v>6.068341668315887</v>
       </c>
       <c r="F42" t="n">
-        <v>9.606511329473021</v>
+        <v>9.605604338597519</v>
       </c>
       <c r="G42" t="n">
-        <v>0.315574484168953</v>
+        <v>0.3157037170136129</v>
       </c>
       <c r="H42" t="n">
         <v>24</v>
@@ -1531,7 +1531,7 @@
         <v>45717</v>
       </c>
       <c r="B43" t="n">
-        <v>2.283779433848873</v>
+        <v>2.284891237104008</v>
       </c>
       <c r="C43" t="n">
         <v>24</v>
@@ -1540,13 +1540,13 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>3.810854307586081</v>
+        <v>3.812595830859507</v>
       </c>
       <c r="F43" t="n">
-        <v>6.266430492348807</v>
+        <v>6.268419497663037</v>
       </c>
       <c r="G43" t="n">
-        <v>0.8084840535419067</v>
+        <v>0.8083624574626243</v>
       </c>
       <c r="H43" t="n">
         <v>24</v>
@@ -1557,7 +1557,7 @@
         <v>45718</v>
       </c>
       <c r="B44" t="n">
-        <v>1.041626952767809</v>
+        <v>1.041614075377196</v>
       </c>
       <c r="C44" t="n">
         <v>24</v>
@@ -1566,13 +1566,13 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>1.868841666666655</v>
+        <v>1.868841666666653</v>
       </c>
       <c r="F44" t="n">
-        <v>3.165559000387077</v>
+        <v>3.16568907144946</v>
       </c>
       <c r="G44" t="n">
-        <v>0.1616006261338926</v>
+        <v>0.161531725988497</v>
       </c>
       <c r="H44" t="n">
         <v>24</v>
@@ -1583,7 +1583,7 @@
         <v>45719</v>
       </c>
       <c r="B45" t="n">
-        <v>1.426970307938108</v>
+        <v>1.425596239991295</v>
       </c>
       <c r="C45" t="n">
         <v>24</v>
@@ -1592,13 +1592,13 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>2.459156709578755</v>
+        <v>2.456733336631759</v>
       </c>
       <c r="F45" t="n">
-        <v>4.252007305555047</v>
+        <v>4.250793488623629</v>
       </c>
       <c r="G45" t="n">
-        <v>0.6547838698359217</v>
+        <v>0.6549809388171017</v>
       </c>
       <c r="H45" t="n">
         <v>24</v>
@@ -1609,7 +1609,7 @@
         <v>45720</v>
       </c>
       <c r="B46" t="n">
-        <v>2.015936125457935</v>
+        <v>2.014885116511277</v>
       </c>
       <c r="C46" t="n">
         <v>24</v>
@@ -1618,13 +1618,13 @@
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>3.32929152574725</v>
+        <v>3.327550002473818</v>
       </c>
       <c r="F46" t="n">
-        <v>4.726234823942326</v>
+        <v>4.725848721317876</v>
       </c>
       <c r="G46" t="n">
-        <v>0.5354948310223189</v>
+        <v>0.5355707220204455</v>
       </c>
       <c r="H46" t="n">
         <v>24</v>
@@ -1635,7 +1635,7 @@
         <v>45721</v>
       </c>
       <c r="B47" t="n">
-        <v>1.03180573179621</v>
+        <v>1.031789080799445</v>
       </c>
       <c r="C47" t="n">
         <v>24</v>
@@ -1644,13 +1644,13 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>1.640279166666671</v>
+        <v>1.640279166666669</v>
       </c>
       <c r="F47" t="n">
-        <v>2.308911492129538</v>
+        <v>2.309077034880346</v>
       </c>
       <c r="G47" t="n">
-        <v>0.7079067937027896</v>
+        <v>0.7078649076049893</v>
       </c>
       <c r="H47" t="n">
         <v>24</v>
@@ -1661,7 +1661,7 @@
         <v>45722</v>
       </c>
       <c r="B48" t="n">
-        <v>0.4462568645758644</v>
+        <v>0.4462463610940372</v>
       </c>
       <c r="C48" t="n">
         <v>24</v>
@@ -1670,13 +1670,13 @@
         <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>0.7109708333333332</v>
+        <v>0.7109708333333357</v>
       </c>
       <c r="F48" t="n">
-        <v>1.426052177546761</v>
+        <v>1.426758825532224</v>
       </c>
       <c r="G48" t="n">
-        <v>0.5851874473390132</v>
+        <v>0.5847762434778923</v>
       </c>
       <c r="H48" t="n">
         <v>24</v>
@@ -1687,7 +1687,7 @@
         <v>45723</v>
       </c>
       <c r="B49" t="n">
-        <v>2.102192149504521</v>
+        <v>2.101073868552693</v>
       </c>
       <c r="C49" t="n">
         <v>24</v>
@@ -1696,13 +1696,13 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>3.323262359080584</v>
+        <v>3.321520835807158</v>
       </c>
       <c r="F49" t="n">
-        <v>5.689497249071655</v>
+        <v>5.689381411905578</v>
       </c>
       <c r="G49" t="n">
-        <v>0.4605284880667685</v>
+        <v>0.4605504549338691</v>
       </c>
       <c r="H49" t="n">
         <v>24</v>
@@ -1713,7 +1713,7 @@
         <v>45724</v>
       </c>
       <c r="B50" t="n">
-        <v>1.927995889181003</v>
+        <v>1.926905444374475</v>
       </c>
       <c r="C50" t="n">
         <v>24</v>
@@ -1722,13 +1722,13 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>3.074504025747254</v>
+        <v>3.072762502473827</v>
       </c>
       <c r="F50" t="n">
-        <v>5.05272514567303</v>
+        <v>5.052639850974485</v>
       </c>
       <c r="G50" t="n">
-        <v>0.3709517261202914</v>
+        <v>0.3709729637805539</v>
       </c>
       <c r="H50" t="n">
         <v>24</v>
@@ -1739,7 +1739,7 @@
         <v>45725</v>
       </c>
       <c r="B51" t="n">
-        <v>2.382659141975327</v>
+        <v>2.382249043876344</v>
       </c>
       <c r="C51" t="n">
         <v>24</v>
@@ -1748,13 +1748,13 @@
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>3.744422175249092</v>
+        <v>3.743841667491282</v>
       </c>
       <c r="F51" t="n">
-        <v>5.030032011571877</v>
+        <v>5.029626918061267</v>
       </c>
       <c r="G51" t="n">
-        <v>0.5681034565145051</v>
+        <v>0.5681730192693663</v>
       </c>
       <c r="H51" t="n">
         <v>24</v>
@@ -1765,7 +1765,7 @@
         <v>45726</v>
       </c>
       <c r="B52" t="n">
-        <v>1.026775134370786</v>
+        <v>1.025987109297065</v>
       </c>
       <c r="C52" t="n">
         <v>24</v>
@@ -1774,13 +1774,13 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>1.649819350498168</v>
+        <v>1.648662500824607</v>
       </c>
       <c r="F52" t="n">
-        <v>3.220925513713072</v>
+        <v>3.221573844903217</v>
       </c>
       <c r="G52" t="n">
-        <v>0.4209832212713218</v>
+        <v>0.4207501004389753</v>
       </c>
       <c r="H52" t="n">
         <v>24</v>
@@ -1791,7 +1791,7 @@
         <v>45727</v>
       </c>
       <c r="B53" t="n">
-        <v>0.9862238207123836</v>
+        <v>0.9854878013593366</v>
       </c>
       <c r="C53" t="n">
         <v>24</v>
@@ -1800,13 +1800,13 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>1.588452683831504</v>
+        <v>1.58729166831588</v>
       </c>
       <c r="F53" t="n">
-        <v>2.904176128894288</v>
+        <v>2.904501697644486</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.1752103959166198</v>
+        <v>-0.1754739014403377</v>
       </c>
       <c r="H53" t="n">
         <v>24</v>
@@ -1817,7 +1817,7 @@
         <v>45728</v>
       </c>
       <c r="B54" t="n">
-        <v>5.252142972539425</v>
+        <v>5.25238784256103</v>
       </c>
       <c r="C54" t="n">
         <v>24</v>
@@ -1826,13 +1826,13 @@
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>7.811323658084246</v>
+        <v>7.811904165842051</v>
       </c>
       <c r="F54" t="n">
-        <v>14.20893855560493</v>
+        <v>14.20891574631406</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.3350680602811014</v>
+        <v>-0.3350637739748217</v>
       </c>
       <c r="H54" t="n">
         <v>24</v>
@@ -1843,7 +1843,7 @@
         <v>45729</v>
       </c>
       <c r="B55" t="n">
-        <v>1.762660489082437</v>
+        <v>1.762666536051678</v>
       </c>
       <c r="C55" t="n">
         <v>24</v>
@@ -1852,13 +1852,13 @@
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>2.512429166666667</v>
+        <v>2.512429166666665</v>
       </c>
       <c r="F55" t="n">
-        <v>5.643696436621018</v>
+        <v>5.64258489473174</v>
       </c>
       <c r="G55" t="n">
-        <v>0.5156035914849089</v>
+        <v>0.5157943791655646</v>
       </c>
       <c r="H55" t="n">
         <v>24</v>
@@ -1869,7 +1869,7 @@
         <v>45730</v>
       </c>
       <c r="B56" t="n">
-        <v>0.7304119571878646</v>
+        <v>0.7317911391597298</v>
       </c>
       <c r="C56" t="n">
         <v>24</v>
@@ -1878,13 +1878,13 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>1.114008474207872</v>
+        <v>1.116037495857539</v>
       </c>
       <c r="F56" t="n">
-        <v>2.311295344935865</v>
+        <v>2.314292202395769</v>
       </c>
       <c r="G56" t="n">
-        <v>0.8465003095244767</v>
+        <v>0.8461019918231055</v>
       </c>
       <c r="H56" t="n">
         <v>24</v>
@@ -1895,7 +1895,7 @@
         <v>45731</v>
       </c>
       <c r="B57" t="n">
-        <v>1.347143718126565</v>
+        <v>1.346025636263558</v>
       </c>
       <c r="C57" t="n">
         <v>24</v>
@@ -1904,13 +1904,13 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>2.083541525625988</v>
+        <v>2.081800001717125</v>
       </c>
       <c r="F57" t="n">
-        <v>3.718694896476848</v>
+        <v>3.71819969032335</v>
       </c>
       <c r="G57" t="n">
-        <v>0.4197380007587165</v>
+        <v>0.4198925335655163</v>
       </c>
       <c r="H57" t="n">
         <v>24</v>
@@ -1921,7 +1921,7 @@
         <v>45732</v>
       </c>
       <c r="B58" t="n">
-        <v>2.339941613619624</v>
+        <v>2.339532580209532</v>
       </c>
       <c r="C58" t="n">
         <v>24</v>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>3.567888840969877</v>
+        <v>3.567308326173782</v>
       </c>
       <c r="F58" t="n">
-        <v>5.675191497692226</v>
+        <v>5.675143942371148</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.02266310669431526</v>
+        <v>-0.02264596793568407</v>
       </c>
       <c r="H58" t="n">
         <v>24</v>
@@ -1947,7 +1947,7 @@
         <v>45733</v>
       </c>
       <c r="B59" t="n">
-        <v>2.907133896033778</v>
+        <v>2.9078773560995</v>
       </c>
       <c r="C59" t="n">
         <v>24</v>
@@ -1956,13 +1956,13 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>4.211088982944303</v>
+        <v>4.21224999907838</v>
       </c>
       <c r="F59" t="n">
-        <v>6.164447891450918</v>
+        <v>6.164007630844769</v>
       </c>
       <c r="G59" t="n">
-        <v>0.4394304492220562</v>
+        <v>0.4395105173421979</v>
       </c>
       <c r="H59" t="n">
         <v>24</v>
@@ -1973,7 +1973,7 @@
         <v>45734</v>
       </c>
       <c r="B60" t="n">
-        <v>7.535666451570809</v>
+        <v>7.535971469235064</v>
       </c>
       <c r="C60" t="n">
         <v>24</v>
@@ -1982,13 +1982,13 @@
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>11.53346949141759</v>
+        <v>11.53404999913659</v>
       </c>
       <c r="F60" t="n">
-        <v>15.54639348987368</v>
+        <v>15.54655570867817</v>
       </c>
       <c r="G60" t="n">
-        <v>0.1125363393536585</v>
+        <v>0.1125178187822807</v>
       </c>
       <c r="H60" t="n">
         <v>24</v>
@@ -1999,7 +1999,7 @@
         <v>45735</v>
       </c>
       <c r="B61" t="n">
-        <v>3.29260001627493</v>
+        <v>3.291409510294882</v>
       </c>
       <c r="C61" t="n">
         <v>24</v>
@@ -2008,13 +2008,13 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>5.185833192413927</v>
+        <v>5.184091669053192</v>
       </c>
       <c r="F61" t="n">
-        <v>7.092083858782339</v>
+        <v>7.091424114184381</v>
       </c>
       <c r="G61" t="n">
-        <v>0.2024353696954879</v>
+        <v>0.2025837504795704</v>
       </c>
       <c r="H61" t="n">
         <v>24</v>
@@ -2025,7 +2025,7 @@
         <v>45736</v>
       </c>
       <c r="B62" t="n">
-        <v>1.919062330349813</v>
+        <v>1.91984457517153</v>
       </c>
       <c r="C62" t="n">
         <v>24</v>
@@ -2034,13 +2034,13 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>2.624138982199728</v>
+        <v>2.625299995876953</v>
       </c>
       <c r="F62" t="n">
-        <v>4.016942431406584</v>
+        <v>4.017133894946518</v>
       </c>
       <c r="G62" t="n">
-        <v>0.3629029738123671</v>
+        <v>0.3628422391809671</v>
       </c>
       <c r="H62" t="n">
         <v>24</v>
@@ -2051,7 +2051,7 @@
         <v>45737</v>
       </c>
       <c r="B63" t="n">
-        <v>3.278011755094318</v>
+        <v>3.277495857378985</v>
       </c>
       <c r="C63" t="n">
         <v>24</v>
@@ -2060,13 +2060,13 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>4.339643008136161</v>
+        <v>4.339062508934878</v>
       </c>
       <c r="F63" t="n">
-        <v>6.663737232506641</v>
+        <v>6.663135473470322</v>
       </c>
       <c r="G63" t="n">
-        <v>0.01869262294155427</v>
+        <v>0.01886984599172892</v>
       </c>
       <c r="H63" t="n">
         <v>24</v>
@@ -2077,7 +2077,7 @@
         <v>45738</v>
       </c>
       <c r="B64" t="n">
-        <v>3.490470191354531</v>
+        <v>3.492394537286107</v>
       </c>
       <c r="C64" t="n">
         <v>24</v>
@@ -2086,13 +2086,13 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>5.333718290421242</v>
+        <v>5.33662082921029</v>
       </c>
       <c r="F64" t="n">
-        <v>6.89958965743388</v>
+        <v>6.901095966854468</v>
       </c>
       <c r="G64" t="n">
-        <v>0.4683748369344241</v>
+        <v>0.4681426841702619</v>
       </c>
       <c r="H64" t="n">
         <v>24</v>
@@ -2103,7 +2103,7 @@
         <v>45739</v>
       </c>
       <c r="B65" t="n">
-        <v>4.464091535840596</v>
+        <v>4.463338387926281</v>
       </c>
       <c r="C65" t="n">
         <v>24</v>
@@ -2112,13 +2112,13 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>6.95356101716484</v>
+        <v>6.952400001649221</v>
       </c>
       <c r="F65" t="n">
-        <v>11.43523802997594</v>
+        <v>11.43587189760818</v>
       </c>
       <c r="G65" t="n">
-        <v>0.6882853680554619</v>
+        <v>0.6882508097382036</v>
       </c>
       <c r="H65" t="n">
         <v>24</v>
@@ -2129,7 +2129,7 @@
         <v>45740</v>
       </c>
       <c r="B66" t="n">
-        <v>3.037442776175557</v>
+        <v>3.036733879646771</v>
       </c>
       <c r="C66" t="n">
         <v>24</v>
@@ -2138,13 +2138,13 @@
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>4.699219350498172</v>
+        <v>4.698058334982552</v>
       </c>
       <c r="F66" t="n">
-        <v>6.422426694793645</v>
+        <v>6.421432996332984</v>
       </c>
       <c r="G66" t="n">
-        <v>0.8512099993657867</v>
+        <v>0.8512560383362628</v>
       </c>
       <c r="H66" t="n">
         <v>24</v>
@@ -2155,7 +2155,7 @@
         <v>45741</v>
       </c>
       <c r="B67" t="n">
-        <v>1.651133448889546</v>
+        <v>1.650363316248721</v>
       </c>
       <c r="C67" t="n">
         <v>24</v>
@@ -2164,13 +2164,13 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>2.413998517164837</v>
+        <v>2.412837501649216</v>
       </c>
       <c r="F67" t="n">
-        <v>3.98071672137282</v>
+        <v>3.979865610976124</v>
       </c>
       <c r="G67" t="n">
-        <v>0.5202038093494968</v>
+        <v>0.5204089562611729</v>
       </c>
       <c r="H67" t="n">
         <v>24</v>
@@ -2181,7 +2181,7 @@
         <v>45742</v>
       </c>
       <c r="B68" t="n">
-        <v>1.085071652315299</v>
+        <v>1.08467017131029</v>
       </c>
       <c r="C68" t="n">
         <v>24</v>
@@ -2190,13 +2190,13 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>1.725613841915757</v>
+        <v>1.725033334157949</v>
       </c>
       <c r="F68" t="n">
-        <v>3.347388392799507</v>
+        <v>3.347397229168816</v>
       </c>
       <c r="G68" t="n">
-        <v>0.5529644620469963</v>
+        <v>0.5529621018928355</v>
       </c>
       <c r="H68" t="n">
         <v>24</v>
@@ -2207,7 +2207,7 @@
         <v>45743</v>
       </c>
       <c r="B69" t="n">
-        <v>2.065138268072005</v>
+        <v>2.064273979382305</v>
       </c>
       <c r="C69" t="n">
         <v>24</v>
@@ -2216,13 +2216,13 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>3.002620692413924</v>
+        <v>3.001366668568117</v>
       </c>
       <c r="F69" t="n">
-        <v>5.035326699920243</v>
+        <v>5.035056593068495</v>
       </c>
       <c r="G69" t="n">
-        <v>0.4979001407790468</v>
+        <v>0.4979540069858748</v>
       </c>
       <c r="H69" t="n">
         <v>24</v>
@@ -2233,7 +2233,7 @@
         <v>45744</v>
       </c>
       <c r="B70" t="n">
-        <v>1.134142855920111</v>
+        <v>1.134900681285686</v>
       </c>
       <c r="C70" t="n">
         <v>24</v>
@@ -2242,13 +2242,13 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>1.710509816027828</v>
+        <v>1.711670770051906</v>
       </c>
       <c r="F70" t="n">
-        <v>3.110677864427826</v>
+        <v>3.110688984753703</v>
       </c>
       <c r="G70" t="n">
-        <v>0.345333180920058</v>
+        <v>0.3453285001901985</v>
       </c>
       <c r="H70" t="n">
         <v>24</v>
@@ -2259,7 +2259,7 @@
         <v>45745</v>
       </c>
       <c r="B71" t="n">
-        <v>1.378646475460128</v>
+        <v>1.379005665555803</v>
       </c>
       <c r="C71" t="n">
         <v>24</v>
@@ -2268,13 +2268,13 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>2.153806991434559</v>
+        <v>2.154387498059749</v>
       </c>
       <c r="F71" t="n">
-        <v>3.55183386703911</v>
+        <v>3.552168573159059</v>
       </c>
       <c r="G71" t="n">
-        <v>0.4820138030608077</v>
+        <v>0.4819161738779449</v>
       </c>
       <c r="H71" t="n">
         <v>24</v>
@@ -2285,7 +2285,7 @@
         <v>45746</v>
       </c>
       <c r="B72" t="n">
-        <v>2.057160412868313</v>
+        <v>2.057834672002889</v>
       </c>
       <c r="C72" t="n">
         <v>24</v>
@@ -2294,13 +2294,13 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>3.215563982855779</v>
+        <v>3.216724998224667</v>
       </c>
       <c r="F72" t="n">
-        <v>4.061370717689154</v>
+        <v>4.062172327203076</v>
       </c>
       <c r="G72" t="n">
-        <v>0.4204847196780912</v>
+        <v>0.4202559344530811</v>
       </c>
       <c r="H72" t="n">
         <v>24</v>
@@ -2311,7 +2311,7 @@
         <v>45747</v>
       </c>
       <c r="B73" t="n">
-        <v>1.62093414463602</v>
+        <v>1.619458240682668</v>
       </c>
       <c r="C73" t="n">
         <v>24</v>
@@ -2320,13 +2320,13 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2.55284286765573</v>
+        <v>2.55052083486614</v>
       </c>
       <c r="F73" t="n">
-        <v>3.975313952128994</v>
+        <v>3.97508220287961</v>
       </c>
       <c r="G73" t="n">
-        <v>0.5208912274061603</v>
+        <v>0.5209470870757641</v>
       </c>
       <c r="H73" t="n">
         <v>24</v>
@@ -2337,7 +2337,7 @@
         <v>45748</v>
       </c>
       <c r="B74" t="n">
-        <v>1.402615807327477</v>
+        <v>1.402984256013552</v>
       </c>
       <c r="C74" t="n">
         <v>24</v>
@@ -2346,13 +2346,13 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>2.120919491409092</v>
+        <v>2.121499997458263</v>
       </c>
       <c r="F74" t="n">
-        <v>4.631688091294783</v>
+        <v>4.630602060624728</v>
       </c>
       <c r="G74" t="n">
-        <v>0.5470307764182487</v>
+        <v>0.5472431744835934</v>
       </c>
       <c r="H74" t="n">
         <v>24</v>
@@ -2363,7 +2363,7 @@
         <v>45749</v>
       </c>
       <c r="B75" t="n">
-        <v>0.156892959536157</v>
+        <v>0.1564856903000351</v>
       </c>
       <c r="C75" t="n">
         <v>24</v>
@@ -2372,13 +2372,13 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>0.2267055085824173</v>
+        <v>0.2261250008246058</v>
       </c>
       <c r="F75" t="n">
-        <v>0.2974547921167874</v>
+        <v>0.296889962064397</v>
       </c>
       <c r="G75" t="n">
-        <v>0.6232095135944482</v>
+        <v>0.6246391125375794</v>
       </c>
       <c r="H75" t="n">
         <v>24</v>
@@ -2389,7 +2389,7 @@
         <v>45750</v>
       </c>
       <c r="B76" t="n">
-        <v>1.25683706037461</v>
+        <v>1.255897380342507</v>
       </c>
       <c r="C76" t="n">
         <v>24</v>
@@ -2398,13 +2398,13 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>1.559215183831506</v>
+        <v>1.558054168315887</v>
       </c>
       <c r="F76" t="n">
-        <v>4.091875235084339</v>
+        <v>4.089873997532168</v>
       </c>
       <c r="G76" t="n">
-        <v>0.8771736347034851</v>
+        <v>0.8772937481536389</v>
       </c>
       <c r="H76" t="n">
         <v>24</v>
@@ -2415,7 +2415,7 @@
         <v>45751</v>
       </c>
       <c r="B77" t="n">
-        <v>0.2070140713685926</v>
+        <v>0.20751715827195</v>
       </c>
       <c r="C77" t="n">
         <v>24</v>
@@ -2424,13 +2424,13 @@
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>0.2377069914175808</v>
+        <v>0.2382874991753899</v>
       </c>
       <c r="F77" t="n">
-        <v>0.3176371637287542</v>
+        <v>0.3168047122144682</v>
       </c>
       <c r="G77" t="n">
-        <v>0.3410675180794581</v>
+        <v>0.3445168031280756</v>
       </c>
       <c r="H77" t="n">
         <v>24</v>
@@ -2441,7 +2441,7 @@
         <v>45752</v>
       </c>
       <c r="B78" t="n">
-        <v>2.388047713789543</v>
+        <v>2.38715760483421</v>
       </c>
       <c r="C78" t="n">
         <v>24</v>
@@ -2450,13 +2450,13 @@
         <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>2.96497069241392</v>
+        <v>2.963791668315884</v>
       </c>
       <c r="F78" t="n">
-        <v>6.431944999456512</v>
+        <v>6.433545389390672</v>
       </c>
       <c r="G78" t="n">
-        <v>0.8851215990286798</v>
+        <v>0.8850644240654935</v>
       </c>
       <c r="H78" t="n">
         <v>24</v>
@@ -2467,7 +2467,7 @@
         <v>45753</v>
       </c>
       <c r="B79" t="n">
-        <v>4.702189324032827</v>
+        <v>4.7030775195429</v>
       </c>
       <c r="C79" t="n">
         <v>24</v>
@@ -2476,13 +2476,13 @@
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>5.569204307586077</v>
+        <v>5.570945830859507</v>
       </c>
       <c r="F79" t="n">
-        <v>14.37093917743014</v>
+        <v>14.3709156679115</v>
       </c>
       <c r="G79" t="n">
-        <v>0.2533811380077144</v>
+        <v>0.2533835808036209</v>
       </c>
       <c r="H79" t="n">
         <v>24</v>
@@ -2493,7 +2493,7 @@
         <v>45754</v>
       </c>
       <c r="B80" t="n">
-        <v>0.1855404580071758</v>
+        <v>0.1866995221574741</v>
       </c>
       <c r="C80" t="n">
         <v>24</v>
@@ -2502,13 +2502,13 @@
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>0.2783293075860769</v>
+        <v>0.2800708308595053</v>
       </c>
       <c r="F80" t="n">
-        <v>0.386842340711399</v>
+        <v>0.3880242382422665</v>
       </c>
       <c r="G80" t="n">
-        <v>0.7516987910032857</v>
+        <v>0.750179231943554</v>
       </c>
       <c r="H80" t="n">
         <v>24</v>
@@ -2519,7 +2519,7 @@
         <v>45755</v>
       </c>
       <c r="B81" t="n">
-        <v>1.186688115849845</v>
+        <v>1.187416975231851</v>
       </c>
       <c r="C81" t="n">
         <v>24</v>
@@ -2528,13 +2528,13 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>1.863805649501834</v>
+        <v>1.864966665017453</v>
       </c>
       <c r="F81" t="n">
-        <v>3.622708535138569</v>
+        <v>3.624313013650173</v>
       </c>
       <c r="G81" t="n">
-        <v>0.6831700112302623</v>
+        <v>0.6828893044187904</v>
       </c>
       <c r="H81" t="n">
         <v>24</v>
@@ -2545,7 +2545,7 @@
         <v>45756</v>
       </c>
       <c r="B82" t="n">
-        <v>2.005538658254392</v>
+        <v>2.00514336279501</v>
       </c>
       <c r="C82" t="n">
         <v>24</v>
@@ -2554,13 +2554,13 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>3.178880508582418</v>
+        <v>3.178300000824611</v>
       </c>
       <c r="F82" t="n">
-        <v>4.710651176825745</v>
+        <v>4.709966167510953</v>
       </c>
       <c r="G82" t="n">
-        <v>0.411343019344779</v>
+        <v>0.411514208499381</v>
       </c>
       <c r="H82" t="n">
         <v>24</v>
@@ -2571,7 +2571,7 @@
         <v>45757</v>
       </c>
       <c r="B83" t="n">
-        <v>2.153230541435568</v>
+        <v>2.153000083220023</v>
       </c>
       <c r="C83" t="n">
         <v>23</v>
@@ -2580,13 +2580,13 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>3.38469635230387</v>
+        <v>3.384393478691107</v>
       </c>
       <c r="F83" t="n">
-        <v>4.801631709615644</v>
+        <v>4.801885294798965</v>
       </c>
       <c r="G83" t="n">
-        <v>0.4408336663245019</v>
+        <v>0.4407746030518056</v>
       </c>
       <c r="H83" t="n">
         <v>23</v>

--- a/optimized_version/metadata/validation_daily_metrics/agus6_validation_daily_metrics.xlsx
+++ b/optimized_version/metadata/validation_daily_metrics/agus6_validation_daily_metrics.xlsx
@@ -467,7 +467,7 @@
         <v>45676</v>
       </c>
       <c r="B2" t="n">
-        <v>0.4098384367763053</v>
+        <v>0.4098384425153208</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -476,10 +476,10 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7066499901046939</v>
+        <v>0.7066499999999962</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7066499901046939</v>
+        <v>0.7066499999999962</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
@@ -491,7 +491,7 @@
         <v>45677</v>
       </c>
       <c r="B3" t="n">
-        <v>7.093870371178868</v>
+        <v>7.093870370886428</v>
       </c>
       <c r="C3" t="n">
         <v>24</v>
@@ -503,10 +503,10 @@
         <v>10.61837083333335</v>
       </c>
       <c r="F3" t="n">
-        <v>17.59718031805072</v>
+        <v>17.59718031702807</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5101199720835492</v>
+        <v>0.5101199721404877</v>
       </c>
       <c r="H3" t="n">
         <v>24</v>
@@ -517,7 +517,7 @@
         <v>45678</v>
       </c>
       <c r="B4" t="n">
-        <v>6.20537495853778</v>
+        <v>6.205374957604476</v>
       </c>
       <c r="C4" t="n">
         <v>24</v>
@@ -526,13 +526,13 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>8.508545834157934</v>
+        <v>8.508545833333324</v>
       </c>
       <c r="F4" t="n">
-        <v>16.85970636483076</v>
+        <v>16.859706365721</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6544809318989928</v>
+        <v>0.6544809318625042</v>
       </c>
       <c r="H4" t="n">
         <v>24</v>
@@ -543,7 +543,7 @@
         <v>45679</v>
       </c>
       <c r="B5" t="n">
-        <v>1.754441324682608</v>
+        <v>1.754441324689283</v>
       </c>
       <c r="C5" t="n">
         <v>24</v>
@@ -555,10 +555,10 @@
         <v>2.965254166666673</v>
       </c>
       <c r="F5" t="n">
-        <v>5.520270494884259</v>
+        <v>5.520270496731419</v>
       </c>
       <c r="G5" t="n">
-        <v>0.823940192455865</v>
+        <v>0.8239401923380409</v>
       </c>
       <c r="H5" t="n">
         <v>24</v>
@@ -569,7 +569,7 @@
         <v>45680</v>
       </c>
       <c r="B6" t="n">
-        <v>1.744309650708601</v>
+        <v>1.744309650696376</v>
       </c>
       <c r="C6" t="n">
         <v>24</v>
@@ -581,10 +581,10 @@
         <v>3.168779166666675</v>
       </c>
       <c r="F6" t="n">
-        <v>5.007771843619645</v>
+        <v>5.007771843345107</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.02980499016472149</v>
+        <v>-0.02980499005180826</v>
       </c>
       <c r="H6" t="n">
         <v>24</v>
@@ -595,7 +595,7 @@
         <v>45681</v>
       </c>
       <c r="B7" t="n">
-        <v>0.6323561432060962</v>
+        <v>0.6323561431959075</v>
       </c>
       <c r="C7" t="n">
         <v>24</v>
@@ -607,10 +607,10 @@
         <v>1.170760416666668</v>
       </c>
       <c r="F7" t="n">
-        <v>2.106747204225634</v>
+        <v>2.106747204395713</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1335190709676511</v>
+        <v>0.1335190708277482</v>
       </c>
       <c r="H7" t="n">
         <v>24</v>
@@ -621,7 +621,7 @@
         <v>45682</v>
       </c>
       <c r="B8" t="n">
-        <v>5.152118223546407</v>
+        <v>5.152118222399194</v>
       </c>
       <c r="C8" t="n">
         <v>24</v>
@@ -630,13 +630,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>4.585460418315893</v>
+        <v>4.585460416666677</v>
       </c>
       <c r="F8" t="n">
-        <v>20.22339401105266</v>
+        <v>20.22339400892719</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6454633421907818</v>
+        <v>0.6454633422653049</v>
       </c>
       <c r="H8" t="n">
         <v>24</v>
@@ -647,7 +647,7 @@
         <v>45683</v>
       </c>
       <c r="B9" t="n">
-        <v>3.492493198708572</v>
+        <v>3.492493200319703</v>
       </c>
       <c r="C9" t="n">
         <v>24</v>
@@ -656,13 +656,13 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>6.046174997526176</v>
+        <v>6.046175000000002</v>
       </c>
       <c r="F9" t="n">
-        <v>17.66381591151254</v>
+        <v>17.66381591410814</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3716705184466663</v>
+        <v>0.3716705182620075</v>
       </c>
       <c r="H9" t="n">
         <v>24</v>
@@ -673,7 +673,7 @@
         <v>45684</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4614155494338943</v>
+        <v>0.461415549000072</v>
       </c>
       <c r="C10" t="n">
         <v>24</v>
@@ -682,13 +682,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8730041674912693</v>
+        <v>0.8730041666666608</v>
       </c>
       <c r="F10" t="n">
-        <v>1.564313612928504</v>
+        <v>1.564313610328293</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7034354115230561</v>
+        <v>0.703435412508959</v>
       </c>
       <c r="H10" t="n">
         <v>24</v>
@@ -699,7 +699,7 @@
         <v>45685</v>
       </c>
       <c r="B11" t="n">
-        <v>1.456176692147493</v>
+        <v>1.456176693841373</v>
       </c>
       <c r="C11" t="n">
         <v>24</v>
@@ -708,13 +708,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>2.684637496701566</v>
+        <v>2.6846375</v>
       </c>
       <c r="F11" t="n">
-        <v>4.098609666787985</v>
+        <v>4.098609668101902</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7215668290049749</v>
+        <v>0.721566828826457</v>
       </c>
       <c r="H11" t="n">
         <v>24</v>
@@ -725,7 +725,7 @@
         <v>45686</v>
       </c>
       <c r="B12" t="n">
-        <v>1.808669429938</v>
+        <v>1.808669429503903</v>
       </c>
       <c r="C12" t="n">
         <v>24</v>
@@ -734,13 +734,13 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>3.169887500824609</v>
+        <v>3.1698875</v>
       </c>
       <c r="F12" t="n">
-        <v>5.529236355990803</v>
+        <v>5.529236355727607</v>
       </c>
       <c r="G12" t="n">
-        <v>0.8768775319138966</v>
+        <v>0.876877531925618</v>
       </c>
       <c r="H12" t="n">
         <v>24</v>
@@ -751,7 +751,7 @@
         <v>45687</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1635776435675619</v>
+        <v>0.1635776444190763</v>
       </c>
       <c r="C13" t="n">
         <v>24</v>
@@ -760,13 +760,13 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3158333316841109</v>
+        <v>0.3158333333333279</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3951241082955356</v>
+        <v>0.3951241091943896</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1018755553764855</v>
+        <v>0.1018755512902624</v>
       </c>
       <c r="H13" t="n">
         <v>24</v>
@@ -777,7 +777,7 @@
         <v>45688</v>
       </c>
       <c r="B14" t="n">
-        <v>2.694622183689466</v>
+        <v>2.694622183696212</v>
       </c>
       <c r="C14" t="n">
         <v>24</v>
@@ -789,10 +789,10 @@
         <v>4.706845833333335</v>
       </c>
       <c r="F14" t="n">
-        <v>8.338257262911531</v>
+        <v>8.338257262412009</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5643242327977571</v>
+        <v>0.5643242328499574</v>
       </c>
       <c r="H14" t="n">
         <v>24</v>
@@ -803,7 +803,7 @@
         <v>45689</v>
       </c>
       <c r="B15" t="n">
-        <v>1.16155867045783</v>
+        <v>1.161558668652546</v>
       </c>
       <c r="C15" t="n">
         <v>24</v>
@@ -812,13 +812,13 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>2.141300003298438</v>
+        <v>2.141300000000003</v>
       </c>
       <c r="F15" t="n">
-        <v>3.083172847078396</v>
+        <v>3.083172846172434</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4451075743244164</v>
+        <v>0.4451075746505163</v>
       </c>
       <c r="H15" t="n">
         <v>24</v>
@@ -829,7 +829,7 @@
         <v>45690</v>
       </c>
       <c r="B16" t="n">
-        <v>9.847088692076786</v>
+        <v>9.847088692862206</v>
       </c>
       <c r="C16" t="n">
         <v>24</v>
@@ -838,13 +838,13 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>13.14121249752617</v>
+        <v>13.14121249999999</v>
       </c>
       <c r="F16" t="n">
-        <v>24.73151149301316</v>
+        <v>24.7315114932347</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5498346489018975</v>
+        <v>0.5498346488938324</v>
       </c>
       <c r="H16" t="n">
         <v>24</v>
@@ -855,7 +855,7 @@
         <v>45691</v>
       </c>
       <c r="B17" t="n">
-        <v>0.2699365583203097</v>
+        <v>0.2699365583144006</v>
       </c>
       <c r="C17" t="n">
         <v>24</v>
@@ -867,10 +867,10 @@
         <v>0.5067708333333284</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8309929439121355</v>
+        <v>0.8309929432111131</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3401601459957311</v>
+        <v>-0.3401601437346233</v>
       </c>
       <c r="H17" t="n">
         <v>24</v>
@@ -881,7 +881,7 @@
         <v>45692</v>
       </c>
       <c r="B18" t="n">
-        <v>1.106558736846254</v>
+        <v>1.106558736362441</v>
       </c>
       <c r="C18" t="n">
         <v>24</v>
@@ -890,13 +890,13 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>2.020783334157944</v>
+        <v>2.020783333333335</v>
       </c>
       <c r="F18" t="n">
-        <v>4.038648378108296</v>
+        <v>4.03864837806743</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.4754412804647348</v>
+        <v>-0.4754412804348753</v>
       </c>
       <c r="H18" t="n">
         <v>24</v>
@@ -907,7 +907,7 @@
         <v>45693</v>
       </c>
       <c r="B19" t="n">
-        <v>2.459983660376677</v>
+        <v>2.459983661267507</v>
       </c>
       <c r="C19" t="n">
         <v>24</v>
@@ -916,13 +916,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>4.129958331684123</v>
+        <v>4.129958333333341</v>
       </c>
       <c r="F19" t="n">
-        <v>8.32556854867007</v>
+        <v>8.325568548403568</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2626773383864613</v>
+        <v>0.2626773384336647</v>
       </c>
       <c r="H19" t="n">
         <v>24</v>
@@ -933,7 +933,7 @@
         <v>45694</v>
       </c>
       <c r="B20" t="n">
-        <v>3.677184854108761</v>
+        <v>3.677184853068324</v>
       </c>
       <c r="C20" t="n">
         <v>24</v>
@@ -942,13 +942,13 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>6.105455557204778</v>
+        <v>6.105455555555561</v>
       </c>
       <c r="F20" t="n">
-        <v>7.885272920400323</v>
+        <v>7.885272918962782</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6347544087354428</v>
+        <v>0.6347544088686163</v>
       </c>
       <c r="H20" t="n">
         <v>24</v>
@@ -959,7 +959,7 @@
         <v>45695</v>
       </c>
       <c r="B21" t="n">
-        <v>3.496197151058458</v>
+        <v>3.496197152277234</v>
       </c>
       <c r="C21" t="n">
         <v>24</v>
@@ -968,13 +968,13 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>5.822912497526165</v>
+        <v>5.82291249999999</v>
       </c>
       <c r="F21" t="n">
-        <v>9.209050131755637</v>
+        <v>9.209050133462462</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6562879980723157</v>
+        <v>0.6562879979449071</v>
       </c>
       <c r="H21" t="n">
         <v>24</v>
@@ -985,7 +985,7 @@
         <v>45696</v>
       </c>
       <c r="B22" t="n">
-        <v>3.351572242135043</v>
+        <v>3.351572242608154</v>
       </c>
       <c r="C22" t="n">
         <v>24</v>
@@ -994,13 +994,13 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>5.582374999175395</v>
+        <v>5.582375000000003</v>
       </c>
       <c r="F22" t="n">
-        <v>8.633655905681394</v>
+        <v>8.633655905657335</v>
       </c>
       <c r="G22" t="n">
-        <v>0.7738707167158196</v>
+        <v>0.77387071671708</v>
       </c>
       <c r="H22" t="n">
         <v>24</v>
@@ -1011,7 +1011,7 @@
         <v>45697</v>
       </c>
       <c r="B23" t="n">
-        <v>9.235977965186541</v>
+        <v>9.235977963121456</v>
       </c>
       <c r="C23" t="n">
         <v>24</v>
@@ -1020,13 +1020,13 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>12.80304166914049</v>
+        <v>12.80304166666666</v>
       </c>
       <c r="F23" t="n">
-        <v>19.72780772104045</v>
+        <v>19.72780772003696</v>
       </c>
       <c r="G23" t="n">
-        <v>0.385611051133302</v>
+        <v>0.3856110511958059</v>
       </c>
       <c r="H23" t="n">
         <v>24</v>
@@ -1037,7 +1037,7 @@
         <v>45698</v>
       </c>
       <c r="B24" t="n">
-        <v>2.633510230336097</v>
+        <v>2.633510230283889</v>
       </c>
       <c r="C24" t="n">
         <v>24</v>
@@ -1049,10 +1049,10 @@
         <v>4.408404166666667</v>
       </c>
       <c r="F24" t="n">
-        <v>6.366445341626999</v>
+        <v>6.366445344669709</v>
       </c>
       <c r="G24" t="n">
-        <v>0.843275460356815</v>
+        <v>0.8432754602070085</v>
       </c>
       <c r="H24" t="n">
         <v>24</v>
@@ -1063,7 +1063,7 @@
         <v>45699</v>
       </c>
       <c r="B25" t="n">
-        <v>4.246786038112093</v>
+        <v>4.246786037774757</v>
       </c>
       <c r="C25" t="n">
         <v>24</v>
@@ -1072,13 +1072,13 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>6.864783334157944</v>
+        <v>6.864783333333335</v>
       </c>
       <c r="F25" t="n">
-        <v>11.02096953787275</v>
+        <v>11.02096953728058</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5626729940574225</v>
+        <v>0.5626729941044184</v>
       </c>
       <c r="H25" t="n">
         <v>24</v>
@@ -1089,7 +1089,7 @@
         <v>45700</v>
       </c>
       <c r="B26" t="n">
-        <v>3.317078980750245</v>
+        <v>3.317078980606263</v>
       </c>
       <c r="C26" t="n">
         <v>24</v>
@@ -1101,10 +1101,10 @@
         <v>5.078654166666657</v>
       </c>
       <c r="F26" t="n">
-        <v>7.598656673528351</v>
+        <v>7.598656672399398</v>
       </c>
       <c r="G26" t="n">
-        <v>0.5551354978000337</v>
+        <v>0.5551354979322232</v>
       </c>
       <c r="H26" t="n">
         <v>24</v>
@@ -1115,7 +1115,7 @@
         <v>45701</v>
       </c>
       <c r="B27" t="n">
-        <v>0.7250059641005037</v>
+        <v>0.7250059651705917</v>
       </c>
       <c r="C27" t="n">
         <v>24</v>
@@ -1124,13 +1124,13 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>1.08165416501745</v>
+        <v>1.081654166666667</v>
       </c>
       <c r="F27" t="n">
-        <v>2.211888699297505</v>
+        <v>2.211888698789648</v>
       </c>
       <c r="G27" t="n">
-        <v>-1.023298242134372</v>
+        <v>-1.023298241205259</v>
       </c>
       <c r="H27" t="n">
         <v>24</v>
@@ -1141,7 +1141,7 @@
         <v>45702</v>
       </c>
       <c r="B28" t="n">
-        <v>2.949392453909811</v>
+        <v>2.949392453768386</v>
       </c>
       <c r="C28" t="n">
         <v>24</v>
@@ -1153,10 +1153,10 @@
         <v>4.511629166666668</v>
       </c>
       <c r="F28" t="n">
-        <v>7.341735152727696</v>
+        <v>7.341735152423668</v>
       </c>
       <c r="G28" t="n">
-        <v>0.309705924769482</v>
+        <v>0.3097059248266534</v>
       </c>
       <c r="H28" t="n">
         <v>24</v>
@@ -1167,7 +1167,7 @@
         <v>45703</v>
       </c>
       <c r="B29" t="n">
-        <v>0.9060625897535898</v>
+        <v>0.9060625897342365</v>
       </c>
       <c r="C29" t="n">
         <v>24</v>
@@ -1179,10 +1179,10 @@
         <v>1.357887499999998</v>
       </c>
       <c r="F29" t="n">
-        <v>1.993189467778471</v>
+        <v>1.993189468540303</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2496099950114972</v>
+        <v>0.2496099944378729</v>
       </c>
       <c r="H29" t="n">
         <v>24</v>
@@ -1193,7 +1193,7 @@
         <v>45704</v>
       </c>
       <c r="B30" t="n">
-        <v>2.928448629569478</v>
+        <v>2.928448631166367</v>
       </c>
       <c r="C30" t="n">
         <v>24</v>
@@ -1202,13 +1202,13 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>4.06949866419285</v>
+        <v>4.069498666666676</v>
       </c>
       <c r="F30" t="n">
-        <v>7.056676212749946</v>
+        <v>7.056676212819158</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.1764236915637536</v>
+        <v>-0.1764236915868305</v>
       </c>
       <c r="H30" t="n">
         <v>24</v>
@@ -1219,7 +1219,7 @@
         <v>45705</v>
       </c>
       <c r="B31" t="n">
-        <v>0.5241573700474392</v>
+        <v>0.5241573763548238</v>
       </c>
       <c r="C31" t="n">
         <v>24</v>
@@ -1228,13 +1228,13 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0.83331798997857</v>
+        <v>0.833317999999989</v>
       </c>
       <c r="F31" t="n">
-        <v>0.83331798997857</v>
+        <v>0.833317999999989</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9787933209588127</v>
+        <v>0.9787933204487528</v>
       </c>
       <c r="H31" t="n">
         <v>24</v>
@@ -1245,7 +1245,7 @@
         <v>45706</v>
       </c>
       <c r="B32" t="n">
-        <v>0.8392756249108254</v>
+        <v>0.8392756263286341</v>
       </c>
       <c r="C32" t="n">
         <v>24</v>
@@ -1254,13 +1254,13 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>1.400737497526161</v>
+        <v>1.400737499999986</v>
       </c>
       <c r="F32" t="n">
-        <v>2.035836419507035</v>
+        <v>2.035836420859972</v>
       </c>
       <c r="G32" t="n">
-        <v>0.605175516613438</v>
+        <v>0.6051755160886685</v>
       </c>
       <c r="H32" t="n">
         <v>24</v>
@@ -1271,7 +1271,7 @@
         <v>45707</v>
       </c>
       <c r="B33" t="n">
-        <v>2.241615477311561</v>
+        <v>2.241615477690159</v>
       </c>
       <c r="C33" t="n">
         <v>24</v>
@@ -1280,13 +1280,13 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>3.581483332508721</v>
+        <v>3.58148333333333</v>
       </c>
       <c r="F33" t="n">
-        <v>6.18504037469657</v>
+        <v>6.185040375306102</v>
       </c>
       <c r="G33" t="n">
-        <v>0.7172381259596858</v>
+        <v>0.7172381259039536</v>
       </c>
       <c r="H33" t="n">
         <v>24</v>
@@ -1297,7 +1297,7 @@
         <v>45708</v>
       </c>
       <c r="B34" t="n">
-        <v>1.565564378727879</v>
+        <v>1.565564376823166</v>
       </c>
       <c r="C34" t="n">
         <v>24</v>
@@ -1306,13 +1306,13 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>2.567270836631765</v>
+        <v>2.567270833333331</v>
       </c>
       <c r="F34" t="n">
-        <v>5.4884223727951</v>
+        <v>5.488422371380205</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5986220282287954</v>
+        <v>0.5986220284357429</v>
       </c>
       <c r="H34" t="n">
         <v>24</v>
@@ -1323,7 +1323,7 @@
         <v>45709</v>
       </c>
       <c r="B35" t="n">
-        <v>2.302752725583315</v>
+        <v>2.302752725650937</v>
       </c>
       <c r="C35" t="n">
         <v>24</v>
@@ -1335,10 +1335,10 @@
         <v>3.587454166666665</v>
       </c>
       <c r="F35" t="n">
-        <v>5.737578888410883</v>
+        <v>5.737578886567341</v>
       </c>
       <c r="G35" t="n">
-        <v>0.7692492334907766</v>
+        <v>0.7692492336390616</v>
       </c>
       <c r="H35" t="n">
         <v>24</v>
@@ -1349,7 +1349,7 @@
         <v>45710</v>
       </c>
       <c r="B36" t="n">
-        <v>2.636489898568224</v>
+        <v>2.636489898104379</v>
       </c>
       <c r="C36" t="n">
         <v>24</v>
@@ -1358,13 +1358,13 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>4.459587500824605</v>
+        <v>4.459587499999997</v>
       </c>
       <c r="F36" t="n">
-        <v>6.703475435993743</v>
+        <v>6.703475437910296</v>
       </c>
       <c r="G36" t="n">
-        <v>0.198702333465693</v>
+        <v>0.198702333007504</v>
       </c>
       <c r="H36" t="n">
         <v>24</v>
@@ -1375,7 +1375,7 @@
         <v>45711</v>
       </c>
       <c r="B37" t="n">
-        <v>2.67175656334641</v>
+        <v>2.671756563243231</v>
       </c>
       <c r="C37" t="n">
         <v>24</v>
@@ -1384,13 +1384,13 @@
         <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>4.197066666686062</v>
+        <v>4.19706666666666</v>
       </c>
       <c r="F37" t="n">
-        <v>7.639230823343818</v>
+        <v>7.639230823041559</v>
       </c>
       <c r="G37" t="n">
-        <v>0.7092176510930549</v>
+        <v>0.7092176511160655</v>
       </c>
       <c r="H37" t="n">
         <v>24</v>
@@ -1401,7 +1401,7 @@
         <v>45712</v>
       </c>
       <c r="B38" t="n">
-        <v>2.920884993679065</v>
+        <v>2.920884993125257</v>
       </c>
       <c r="C38" t="n">
         <v>24</v>
@@ -1410,13 +1410,13 @@
         <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>4.584258334157944</v>
+        <v>4.584258333333335</v>
       </c>
       <c r="F38" t="n">
-        <v>6.553267720191659</v>
+        <v>6.553267720127617</v>
       </c>
       <c r="G38" t="n">
-        <v>0.616887053327818</v>
+        <v>0.6168870533353059</v>
       </c>
       <c r="H38" t="n">
         <v>24</v>
@@ -1427,7 +1427,7 @@
         <v>45713</v>
       </c>
       <c r="B39" t="n">
-        <v>2.189587673452402</v>
+        <v>2.189587671146405</v>
       </c>
       <c r="C39" t="n">
         <v>24</v>
@@ -1436,13 +1436,13 @@
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>3.064212503298438</v>
+        <v>3.064212500000004</v>
       </c>
       <c r="F39" t="n">
-        <v>5.250703279683045</v>
+        <v>5.250703277260426</v>
       </c>
       <c r="G39" t="n">
-        <v>0.7012483914032865</v>
+        <v>0.7012483916789682</v>
       </c>
       <c r="H39" t="n">
         <v>24</v>
@@ -1453,7 +1453,7 @@
         <v>45714</v>
       </c>
       <c r="B40" t="n">
-        <v>1.58184681258601</v>
+        <v>1.581846813285638</v>
       </c>
       <c r="C40" t="n">
         <v>24</v>
@@ -1462,13 +1462,13 @@
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>2.584574999175396</v>
+        <v>2.584575000000005</v>
       </c>
       <c r="F40" t="n">
-        <v>4.630127144439356</v>
+        <v>4.630127148992059</v>
       </c>
       <c r="G40" t="n">
-        <v>0.9446725925167739</v>
+        <v>0.9446725924079695</v>
       </c>
       <c r="H40" t="n">
         <v>24</v>
@@ -1479,7 +1479,7 @@
         <v>45715</v>
       </c>
       <c r="B41" t="n">
-        <v>2.664720719119697</v>
+        <v>2.664720718604767</v>
       </c>
       <c r="C41" t="n">
         <v>24</v>
@@ -1488,13 +1488,13 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>4.475825000824609</v>
+        <v>4.475825</v>
       </c>
       <c r="F41" t="n">
-        <v>8.708646487700662</v>
+        <v>8.708646487016987</v>
       </c>
       <c r="G41" t="n">
-        <v>0.4526962669399194</v>
+        <v>0.4526962670258519</v>
       </c>
       <c r="H41" t="n">
         <v>24</v>
@@ -1505,7 +1505,7 @@
         <v>45716</v>
       </c>
       <c r="B42" t="n">
-        <v>3.721471989789384</v>
+        <v>3.721471988757292</v>
       </c>
       <c r="C42" t="n">
         <v>24</v>
@@ -1514,13 +1514,13 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>6.068341668315887</v>
+        <v>6.06834166666667</v>
       </c>
       <c r="F42" t="n">
-        <v>9.605604338597519</v>
+        <v>9.605604337312672</v>
       </c>
       <c r="G42" t="n">
-        <v>0.3157037170136129</v>
+        <v>0.3157037171966762</v>
       </c>
       <c r="H42" t="n">
         <v>24</v>
@@ -1531,7 +1531,7 @@
         <v>45717</v>
       </c>
       <c r="B43" t="n">
-        <v>2.284891237104008</v>
+        <v>2.284891238683318</v>
       </c>
       <c r="C43" t="n">
         <v>24</v>
@@ -1540,13 +1540,13 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>3.812595830859507</v>
+        <v>3.812595833333333</v>
       </c>
       <c r="F43" t="n">
-        <v>6.268419497663037</v>
+        <v>6.26841950049346</v>
       </c>
       <c r="G43" t="n">
-        <v>0.8083624574626243</v>
+        <v>0.8083624572895615</v>
       </c>
       <c r="H43" t="n">
         <v>24</v>
@@ -1557,7 +1557,7 @@
         <v>45718</v>
       </c>
       <c r="B44" t="n">
-        <v>1.041614075377196</v>
+        <v>1.041614075358903</v>
       </c>
       <c r="C44" t="n">
         <v>24</v>
@@ -1569,10 +1569,10 @@
         <v>1.868841666666653</v>
       </c>
       <c r="F44" t="n">
-        <v>3.16568907144946</v>
+        <v>3.165689071645109</v>
       </c>
       <c r="G44" t="n">
-        <v>0.161531725988497</v>
+        <v>0.1615317258848573</v>
       </c>
       <c r="H44" t="n">
         <v>24</v>
@@ -1583,7 +1583,7 @@
         <v>45719</v>
       </c>
       <c r="B45" t="n">
-        <v>1.425596239991295</v>
+        <v>1.425596238118363</v>
       </c>
       <c r="C45" t="n">
         <v>24</v>
@@ -1592,13 +1592,13 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>2.456733336631759</v>
+        <v>2.456733333333325</v>
       </c>
       <c r="F45" t="n">
-        <v>4.250793488623629</v>
+        <v>4.25079348690727</v>
       </c>
       <c r="G45" t="n">
-        <v>0.6549809388171017</v>
+        <v>0.6549809390957212</v>
       </c>
       <c r="H45" t="n">
         <v>24</v>
@@ -1609,7 +1609,7 @@
         <v>45720</v>
       </c>
       <c r="B46" t="n">
-        <v>2.014885116511277</v>
+        <v>2.014885115018324</v>
       </c>
       <c r="C46" t="n">
         <v>24</v>
@@ -1618,13 +1618,13 @@
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>3.327550002473818</v>
+        <v>3.327549999999993</v>
       </c>
       <c r="F46" t="n">
-        <v>4.725848721317876</v>
+        <v>4.725848720776689</v>
       </c>
       <c r="G46" t="n">
-        <v>0.5355707220204455</v>
+        <v>0.5355707221268149</v>
       </c>
       <c r="H46" t="n">
         <v>24</v>
@@ -1635,7 +1635,7 @@
         <v>45721</v>
       </c>
       <c r="B47" t="n">
-        <v>1.031789080799445</v>
+        <v>1.031789080775792</v>
       </c>
       <c r="C47" t="n">
         <v>24</v>
@@ -1647,10 +1647,10 @@
         <v>1.640279166666669</v>
       </c>
       <c r="F47" t="n">
-        <v>2.309077034880346</v>
+        <v>2.309077035130417</v>
       </c>
       <c r="G47" t="n">
-        <v>0.7078649076049893</v>
+        <v>0.7078649075417136</v>
       </c>
       <c r="H47" t="n">
         <v>24</v>
@@ -1661,7 +1661,7 @@
         <v>45722</v>
       </c>
       <c r="B48" t="n">
-        <v>0.4462463610940372</v>
+        <v>0.446246361079117</v>
       </c>
       <c r="C48" t="n">
         <v>24</v>
@@ -1673,10 +1673,10 @@
         <v>0.7109708333333357</v>
       </c>
       <c r="F48" t="n">
-        <v>1.426758825532224</v>
+        <v>1.426758826559923</v>
       </c>
       <c r="G48" t="n">
-        <v>0.5847762434778923</v>
+        <v>0.5847762428797186</v>
       </c>
       <c r="H48" t="n">
         <v>24</v>
@@ -1687,7 +1687,7 @@
         <v>45723</v>
       </c>
       <c r="B49" t="n">
-        <v>2.101073868552693</v>
+        <v>2.10107386696418</v>
       </c>
       <c r="C49" t="n">
         <v>24</v>
@@ -1696,13 +1696,13 @@
         <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>3.321520835807158</v>
+        <v>3.321520833333332</v>
       </c>
       <c r="F49" t="n">
-        <v>5.689381411905578</v>
+        <v>5.689381411747089</v>
       </c>
       <c r="G49" t="n">
-        <v>0.4605504549338691</v>
+        <v>0.4605504549639241</v>
       </c>
       <c r="H49" t="n">
         <v>24</v>
@@ -1713,7 +1713,7 @@
         <v>45724</v>
       </c>
       <c r="B50" t="n">
-        <v>1.926905444374475</v>
+        <v>1.926905442825503</v>
       </c>
       <c r="C50" t="n">
         <v>24</v>
@@ -1722,13 +1722,13 @@
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>3.072762502473827</v>
+        <v>3.072762500000001</v>
       </c>
       <c r="F50" t="n">
-        <v>5.052639850974485</v>
+        <v>5.052639850860144</v>
       </c>
       <c r="G50" t="n">
-        <v>0.3709729637805539</v>
+        <v>0.3709729638090234</v>
       </c>
       <c r="H50" t="n">
         <v>24</v>
@@ -1739,7 +1739,7 @@
         <v>45725</v>
       </c>
       <c r="B51" t="n">
-        <v>2.382249043876344</v>
+        <v>2.382249043293802</v>
       </c>
       <c r="C51" t="n">
         <v>24</v>
@@ -1748,13 +1748,13 @@
         <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>3.743841667491282</v>
+        <v>3.743841666666673</v>
       </c>
       <c r="F51" t="n">
-        <v>5.029626918061267</v>
+        <v>5.029626917492663</v>
       </c>
       <c r="G51" t="n">
-        <v>0.5681730192693663</v>
+        <v>0.5681730193670032</v>
       </c>
       <c r="H51" t="n">
         <v>24</v>
@@ -1765,7 +1765,7 @@
         <v>45726</v>
       </c>
       <c r="B52" t="n">
-        <v>1.025987109297065</v>
+        <v>1.025987108703863</v>
       </c>
       <c r="C52" t="n">
         <v>24</v>
@@ -1774,13 +1774,13 @@
         <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>1.648662500824607</v>
+        <v>1.648662499999998</v>
       </c>
       <c r="F52" t="n">
-        <v>3.221573844903217</v>
+        <v>3.221573845834774</v>
       </c>
       <c r="G52" t="n">
-        <v>0.4207501004389753</v>
+        <v>0.4207501001039811</v>
       </c>
       <c r="H52" t="n">
         <v>24</v>
@@ -1791,7 +1791,7 @@
         <v>45727</v>
       </c>
       <c r="B53" t="n">
-        <v>0.9854878013593366</v>
+        <v>0.9854878003138245</v>
       </c>
       <c r="C53" t="n">
         <v>24</v>
@@ -1800,13 +1800,13 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>1.58729166831588</v>
+        <v>1.587291666666663</v>
       </c>
       <c r="F53" t="n">
-        <v>2.904501697644486</v>
+        <v>2.904501698118795</v>
       </c>
       <c r="G53" t="n">
-        <v>-0.1754739014403377</v>
+        <v>-0.1754739018242508</v>
       </c>
       <c r="H53" t="n">
         <v>24</v>
@@ -1817,7 +1817,7 @@
         <v>45728</v>
       </c>
       <c r="B54" t="n">
-        <v>5.25238784256103</v>
+        <v>5.252387842908866</v>
       </c>
       <c r="C54" t="n">
         <v>24</v>
@@ -1826,13 +1826,13 @@
         <v>0</v>
       </c>
       <c r="E54" t="n">
-        <v>7.811904165842051</v>
+        <v>7.81190416666666</v>
       </c>
       <c r="F54" t="n">
-        <v>14.20891574631406</v>
+        <v>14.20891574628408</v>
       </c>
       <c r="G54" t="n">
-        <v>-0.3350637739748217</v>
+        <v>-0.3350637739691884</v>
       </c>
       <c r="H54" t="n">
         <v>24</v>
@@ -1843,7 +1843,7 @@
         <v>45729</v>
       </c>
       <c r="B55" t="n">
-        <v>1.762666536051678</v>
+        <v>1.762666536059576</v>
       </c>
       <c r="C55" t="n">
         <v>24</v>
@@ -1855,10 +1855,10 @@
         <v>2.512429166666665</v>
       </c>
       <c r="F55" t="n">
-        <v>5.64258489473174</v>
+        <v>5.642584893099379</v>
       </c>
       <c r="G55" t="n">
-        <v>0.5157943791655646</v>
+        <v>0.5157943794457193</v>
       </c>
       <c r="H55" t="n">
         <v>24</v>
@@ -1869,7 +1869,7 @@
         <v>45730</v>
       </c>
       <c r="B56" t="n">
-        <v>0.7317911391597298</v>
+        <v>0.7317911418978278</v>
       </c>
       <c r="C56" t="n">
         <v>24</v>
@@ -1878,13 +1878,13 @@
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>1.116037495857539</v>
+        <v>1.116037499932075</v>
       </c>
       <c r="F56" t="n">
-        <v>2.314292202395769</v>
+        <v>2.31429220924823</v>
       </c>
       <c r="G56" t="n">
-        <v>0.8461019918231055</v>
+        <v>0.8461019909117425</v>
       </c>
       <c r="H56" t="n">
         <v>24</v>
@@ -1895,7 +1895,7 @@
         <v>45731</v>
       </c>
       <c r="B57" t="n">
-        <v>1.346025636263558</v>
+        <v>1.346025635155721</v>
       </c>
       <c r="C57" t="n">
         <v>24</v>
@@ -1904,13 +1904,13 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
-        <v>2.081800001717125</v>
+        <v>2.081799999999999</v>
       </c>
       <c r="F57" t="n">
-        <v>3.71819969032335</v>
+        <v>3.718199689701988</v>
       </c>
       <c r="G57" t="n">
-        <v>0.4198925335655163</v>
+        <v>0.4198925337594042</v>
       </c>
       <c r="H57" t="n">
         <v>24</v>
@@ -1921,7 +1921,7 @@
         <v>45732</v>
       </c>
       <c r="B58" t="n">
-        <v>2.339532580209532</v>
+        <v>2.339532584655385</v>
       </c>
       <c r="C58" t="n">
         <v>24</v>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>3.567308326173782</v>
+        <v>3.567308333333325</v>
       </c>
       <c r="F58" t="n">
-        <v>5.675143942371148</v>
+        <v>5.67514394386095</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.02264596793568407</v>
+        <v>-0.02264596847260036</v>
       </c>
       <c r="H58" t="n">
         <v>24</v>
@@ -1947,7 +1947,7 @@
         <v>45733</v>
       </c>
       <c r="B59" t="n">
-        <v>2.9078773560995</v>
+        <v>2.9078773566531</v>
       </c>
       <c r="C59" t="n">
         <v>24</v>
@@ -1956,13 +1956,13 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>4.21224999907838</v>
+        <v>4.212250000000001</v>
       </c>
       <c r="F59" t="n">
-        <v>6.164007630844769</v>
+        <v>6.16400762925726</v>
       </c>
       <c r="G59" t="n">
-        <v>0.4395105173421979</v>
+        <v>0.4395105176309004</v>
       </c>
       <c r="H59" t="n">
         <v>24</v>
@@ -1973,7 +1973,7 @@
         <v>45734</v>
       </c>
       <c r="B60" t="n">
-        <v>7.535971469235064</v>
+        <v>7.535971469692539</v>
       </c>
       <c r="C60" t="n">
         <v>24</v>
@@ -1982,13 +1982,13 @@
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>11.53404999913659</v>
+        <v>11.53405000000001</v>
       </c>
       <c r="F60" t="n">
-        <v>15.54655570867817</v>
+        <v>15.54655570892902</v>
       </c>
       <c r="G60" t="n">
-        <v>0.1125178187822807</v>
+        <v>0.1125178187536408</v>
       </c>
       <c r="H60" t="n">
         <v>24</v>
@@ -1999,7 +1999,7 @@
         <v>45735</v>
       </c>
       <c r="B61" t="n">
-        <v>3.291409510294882</v>
+        <v>3.291409508660826</v>
       </c>
       <c r="C61" t="n">
         <v>24</v>
@@ -2008,13 +2008,13 @@
         <v>0</v>
       </c>
       <c r="E61" t="n">
-        <v>5.184091669053192</v>
+        <v>5.184091666666678</v>
       </c>
       <c r="F61" t="n">
-        <v>7.091424114184381</v>
+        <v>7.091424113380431</v>
       </c>
       <c r="G61" t="n">
-        <v>0.2025837504795704</v>
+        <v>0.2025837506603755</v>
       </c>
       <c r="H61" t="n">
         <v>24</v>
@@ -2025,7 +2025,7 @@
         <v>45736</v>
       </c>
       <c r="B62" t="n">
-        <v>1.91984457517153</v>
+        <v>1.919844573478317</v>
       </c>
       <c r="C62" t="n">
         <v>24</v>
@@ -2034,13 +2034,13 @@
         <v>0</v>
       </c>
       <c r="E62" t="n">
-        <v>2.625299995876953</v>
+        <v>2.625299993529244</v>
       </c>
       <c r="F62" t="n">
-        <v>4.017133894946518</v>
+        <v>4.017133897212146</v>
       </c>
       <c r="G62" t="n">
-        <v>0.3628422391809671</v>
+        <v>0.3628422384622645</v>
       </c>
       <c r="H62" t="n">
         <v>24</v>
@@ -2051,7 +2051,7 @@
         <v>45737</v>
       </c>
       <c r="B63" t="n">
-        <v>3.277495857378985</v>
+        <v>3.277495846103081</v>
       </c>
       <c r="C63" t="n">
         <v>24</v>
@@ -2060,13 +2060,13 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>4.339062508934878</v>
+        <v>4.339062493209108</v>
       </c>
       <c r="F63" t="n">
-        <v>6.663135473470322</v>
+        <v>6.66313547175444</v>
       </c>
       <c r="G63" t="n">
-        <v>0.01886984599172892</v>
+        <v>0.01886984649704804</v>
       </c>
       <c r="H63" t="n">
         <v>24</v>
@@ -2077,7 +2077,7 @@
         <v>45738</v>
       </c>
       <c r="B64" t="n">
-        <v>3.492394537286107</v>
+        <v>3.492394540019631</v>
       </c>
       <c r="C64" t="n">
         <v>24</v>
@@ -2086,13 +2086,13 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
-        <v>5.33662082921029</v>
+        <v>5.336620833333332</v>
       </c>
       <c r="F64" t="n">
-        <v>6.901095966854468</v>
+        <v>6.901095968998933</v>
       </c>
       <c r="G64" t="n">
-        <v>0.4681426841702619</v>
+        <v>0.4681426838397202</v>
       </c>
       <c r="H64" t="n">
         <v>24</v>
@@ -2103,7 +2103,7 @@
         <v>45739</v>
       </c>
       <c r="B65" t="n">
-        <v>4.463338387926281</v>
+        <v>4.463338386856439</v>
       </c>
       <c r="C65" t="n">
         <v>24</v>
@@ -2112,13 +2112,13 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>6.952400001649221</v>
+        <v>6.952400000000004</v>
       </c>
       <c r="F65" t="n">
-        <v>11.43587189760818</v>
+        <v>11.43587189851157</v>
       </c>
       <c r="G65" t="n">
-        <v>0.6882508097382036</v>
+        <v>0.6882508096889494</v>
       </c>
       <c r="H65" t="n">
         <v>24</v>
@@ -2129,7 +2129,7 @@
         <v>45740</v>
       </c>
       <c r="B66" t="n">
-        <v>3.036733879646771</v>
+        <v>3.036733878639787</v>
       </c>
       <c r="C66" t="n">
         <v>24</v>
@@ -2138,13 +2138,13 @@
         <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>4.698058334982552</v>
+        <v>4.698058333333336</v>
       </c>
       <c r="F66" t="n">
-        <v>6.421432996332984</v>
+        <v>6.421432994926699</v>
       </c>
       <c r="G66" t="n">
-        <v>0.8512560383362628</v>
+        <v>0.8512560384014124</v>
       </c>
       <c r="H66" t="n">
         <v>24</v>
@@ -2155,7 +2155,7 @@
         <v>45741</v>
       </c>
       <c r="B67" t="n">
-        <v>1.650363316248721</v>
+        <v>1.650363315154752</v>
       </c>
       <c r="C67" t="n">
         <v>24</v>
@@ -2164,13 +2164,13 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>2.412837501649216</v>
+        <v>2.412837499999998</v>
       </c>
       <c r="F67" t="n">
-        <v>3.979865610976124</v>
+        <v>3.979865609775656</v>
       </c>
       <c r="G67" t="n">
-        <v>0.5204089562611729</v>
+        <v>0.5204089565504959</v>
       </c>
       <c r="H67" t="n">
         <v>24</v>
@@ -2181,7 +2181,7 @@
         <v>45742</v>
       </c>
       <c r="B68" t="n">
-        <v>1.08467017131029</v>
+        <v>1.084670170739988</v>
       </c>
       <c r="C68" t="n">
         <v>24</v>
@@ -2190,13 +2190,13 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>1.725033334157949</v>
+        <v>1.725033333333341</v>
       </c>
       <c r="F68" t="n">
-        <v>3.347397229168816</v>
+        <v>3.347397229191665</v>
       </c>
       <c r="G68" t="n">
-        <v>0.5529621018928355</v>
+        <v>0.5529621018867328</v>
       </c>
       <c r="H68" t="n">
         <v>24</v>
@@ -2207,7 +2207,7 @@
         <v>45743</v>
       </c>
       <c r="B69" t="n">
-        <v>2.064273979382305</v>
+        <v>2.064273978072893</v>
       </c>
       <c r="C69" t="n">
         <v>24</v>
@@ -2216,13 +2216,13 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>3.001366668568117</v>
+        <v>3.001366666666667</v>
       </c>
       <c r="F69" t="n">
-        <v>5.035056593068495</v>
+        <v>5.035056592511322</v>
       </c>
       <c r="G69" t="n">
-        <v>0.4979540069858748</v>
+        <v>0.4979540070969863</v>
       </c>
       <c r="H69" t="n">
         <v>24</v>
@@ -2233,7 +2233,7 @@
         <v>45744</v>
       </c>
       <c r="B70" t="n">
-        <v>1.134900681285686</v>
+        <v>1.134900723309426</v>
       </c>
       <c r="C70" t="n">
         <v>24</v>
@@ -2242,13 +2242,13 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
-        <v>1.711670770051906</v>
+        <v>1.711670833333335</v>
       </c>
       <c r="F70" t="n">
-        <v>3.110688984753703</v>
+        <v>3.110688996830122</v>
       </c>
       <c r="G70" t="n">
-        <v>0.3453285001901985</v>
+        <v>0.345328495107024</v>
       </c>
       <c r="H70" t="n">
         <v>24</v>
@@ -2259,7 +2259,7 @@
         <v>45745</v>
       </c>
       <c r="B71" t="n">
-        <v>1.379005665555803</v>
+        <v>1.379005666809764</v>
       </c>
       <c r="C71" t="n">
         <v>24</v>
@@ -2268,13 +2268,13 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>2.154387498059749</v>
+        <v>2.154387500000004</v>
       </c>
       <c r="F71" t="n">
-        <v>3.552168573159059</v>
+        <v>3.55216857520398</v>
       </c>
       <c r="G71" t="n">
-        <v>0.4819161738779449</v>
+        <v>0.4819161732814418</v>
       </c>
       <c r="H71" t="n">
         <v>24</v>
@@ -2285,7 +2285,7 @@
         <v>45746</v>
       </c>
       <c r="B72" t="n">
-        <v>2.057834672002889</v>
+        <v>2.057834673055863</v>
       </c>
       <c r="C72" t="n">
         <v>24</v>
@@ -2294,13 +2294,13 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>3.216724998224667</v>
+        <v>3.216725</v>
       </c>
       <c r="F72" t="n">
-        <v>4.062172327203076</v>
+        <v>4.062172328118704</v>
       </c>
       <c r="G72" t="n">
-        <v>0.4202559344530811</v>
+        <v>0.4202559341917282</v>
       </c>
       <c r="H72" t="n">
         <v>24</v>
@@ -2311,7 +2311,7 @@
         <v>45747</v>
       </c>
       <c r="B73" t="n">
-        <v>1.619458240682668</v>
+        <v>1.619458239682597</v>
       </c>
       <c r="C73" t="n">
         <v>24</v>
@@ -2320,13 +2320,13 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>2.55052083486614</v>
+        <v>2.550520833333338</v>
       </c>
       <c r="F73" t="n">
-        <v>3.97508220287961</v>
+        <v>3.975082206173018</v>
       </c>
       <c r="G73" t="n">
-        <v>0.5209470870757641</v>
+        <v>0.5209470862819607</v>
       </c>
       <c r="H73" t="n">
         <v>24</v>
@@ -2337,7 +2337,7 @@
         <v>45748</v>
       </c>
       <c r="B74" t="n">
-        <v>1.402984256013552</v>
+        <v>1.402984257646978</v>
       </c>
       <c r="C74" t="n">
         <v>24</v>
@@ -2346,13 +2346,13 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
-        <v>2.121499997458263</v>
+        <v>2.121500000029101</v>
       </c>
       <c r="F74" t="n">
-        <v>4.630602060624728</v>
+        <v>4.630602063213914</v>
       </c>
       <c r="G74" t="n">
-        <v>0.5472431744835934</v>
+        <v>0.5472431739772785</v>
       </c>
       <c r="H74" t="n">
         <v>24</v>
@@ -2363,7 +2363,7 @@
         <v>45749</v>
       </c>
       <c r="B75" t="n">
-        <v>0.1564856903000351</v>
+        <v>0.1564856897215111</v>
       </c>
       <c r="C75" t="n">
         <v>24</v>
@@ -2372,13 +2372,13 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>0.2261250008246058</v>
+        <v>0.2261249999999973</v>
       </c>
       <c r="F75" t="n">
-        <v>0.296889962064397</v>
+        <v>0.296889961377385</v>
       </c>
       <c r="G75" t="n">
-        <v>0.6246391125375794</v>
+        <v>0.6246391142747715</v>
       </c>
       <c r="H75" t="n">
         <v>24</v>
@@ -2389,7 +2389,7 @@
         <v>45750</v>
       </c>
       <c r="B76" t="n">
-        <v>1.255897380342507</v>
+        <v>1.255897379007695</v>
       </c>
       <c r="C76" t="n">
         <v>24</v>
@@ -2398,13 +2398,13 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>1.558054168315887</v>
+        <v>1.558054166666669</v>
       </c>
       <c r="F76" t="n">
-        <v>4.089873997532168</v>
+        <v>4.089873994697152</v>
       </c>
       <c r="G76" t="n">
-        <v>0.8772937481536389</v>
+        <v>0.8772937483237537</v>
       </c>
       <c r="H76" t="n">
         <v>24</v>
@@ -2415,7 +2415,7 @@
         <v>45751</v>
       </c>
       <c r="B77" t="n">
-        <v>0.20751715827195</v>
+        <v>0.2075171589865825</v>
       </c>
       <c r="C77" t="n">
         <v>24</v>
@@ -2424,13 +2424,13 @@
         <v>0</v>
       </c>
       <c r="E77" t="n">
-        <v>0.2382874991753899</v>
+        <v>0.2382874999999984</v>
       </c>
       <c r="F77" t="n">
-        <v>0.3168047122144682</v>
+        <v>0.3168047111392133</v>
       </c>
       <c r="G77" t="n">
-        <v>0.3445168031280756</v>
+        <v>0.3445168075775772</v>
       </c>
       <c r="H77" t="n">
         <v>24</v>
@@ -2441,7 +2441,7 @@
         <v>45752</v>
       </c>
       <c r="B78" t="n">
-        <v>2.38715760483421</v>
+        <v>2.387157603592156</v>
       </c>
       <c r="C78" t="n">
         <v>24</v>
@@ -2450,13 +2450,13 @@
         <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>2.963791668315884</v>
+        <v>2.963791666666667</v>
       </c>
       <c r="F78" t="n">
-        <v>6.433545389390672</v>
+        <v>6.433545391669093</v>
       </c>
       <c r="G78" t="n">
-        <v>0.8850644240654935</v>
+        <v>0.8850644239840852</v>
       </c>
       <c r="H78" t="n">
         <v>24</v>
@@ -2467,7 +2467,7 @@
         <v>45753</v>
       </c>
       <c r="B79" t="n">
-        <v>4.7030775195429</v>
+        <v>4.703077520804577</v>
       </c>
       <c r="C79" t="n">
         <v>24</v>
@@ -2476,13 +2476,13 @@
         <v>0</v>
       </c>
       <c r="E79" t="n">
-        <v>5.570945830859507</v>
+        <v>5.570945833333332</v>
       </c>
       <c r="F79" t="n">
-        <v>14.3709156679115</v>
+        <v>14.3709156678805</v>
       </c>
       <c r="G79" t="n">
-        <v>0.2533835808036209</v>
+        <v>0.2533835808068418</v>
       </c>
       <c r="H79" t="n">
         <v>24</v>
@@ -2493,7 +2493,7 @@
         <v>45754</v>
       </c>
       <c r="B80" t="n">
-        <v>0.1866995221574741</v>
+        <v>0.1866995238039192</v>
       </c>
       <c r="C80" t="n">
         <v>24</v>
@@ -2502,13 +2502,13 @@
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>0.2800708308595053</v>
+        <v>0.2800708333333309</v>
       </c>
       <c r="F80" t="n">
-        <v>0.3880242382422665</v>
+        <v>0.3880242400074134</v>
       </c>
       <c r="G80" t="n">
-        <v>0.750179231943554</v>
+        <v>0.7501792296706529</v>
       </c>
       <c r="H80" t="n">
         <v>24</v>
@@ -2519,7 +2519,7 @@
         <v>45755</v>
       </c>
       <c r="B81" t="n">
-        <v>1.187416975231851</v>
+        <v>1.187416976267192</v>
       </c>
       <c r="C81" t="n">
         <v>24</v>
@@ -2528,13 +2528,13 @@
         <v>0</v>
       </c>
       <c r="E81" t="n">
-        <v>1.864966665017453</v>
+        <v>1.86496666666667</v>
       </c>
       <c r="F81" t="n">
-        <v>3.624313013650173</v>
+        <v>3.624313015938332</v>
       </c>
       <c r="G81" t="n">
-        <v>0.6828893044187904</v>
+        <v>0.6828893040183835</v>
       </c>
       <c r="H81" t="n">
         <v>24</v>
@@ -2545,7 +2545,7 @@
         <v>45756</v>
       </c>
       <c r="B82" t="n">
-        <v>2.00514336279501</v>
+        <v>2.005143362233495</v>
       </c>
       <c r="C82" t="n">
         <v>24</v>
@@ -2554,13 +2554,13 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>3.178300000824611</v>
+        <v>3.178300000000002</v>
       </c>
       <c r="F82" t="n">
-        <v>4.709966167510953</v>
+        <v>4.709966166545148</v>
       </c>
       <c r="G82" t="n">
-        <v>0.411514208499381</v>
+        <v>0.4115142087407256</v>
       </c>
       <c r="H82" t="n">
         <v>24</v>
@@ -2571,7 +2571,7 @@
         <v>45757</v>
       </c>
       <c r="B83" t="n">
-        <v>2.153000083220023</v>
+        <v>2.153000082892658</v>
       </c>
       <c r="C83" t="n">
         <v>23</v>
@@ -2580,13 +2580,13 @@
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>3.384393478691107</v>
+        <v>3.384393478260877</v>
       </c>
       <c r="F83" t="n">
-        <v>4.801885294798965</v>
+        <v>4.80188529516635</v>
       </c>
       <c r="G83" t="n">
-        <v>0.4407746030518056</v>
+        <v>0.4407746029662346</v>
       </c>
       <c r="H83" t="n">
         <v>23</v>
